--- a/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE49"/>
+  <dimension ref="A1:AE115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5526,6 +5526,6804 @@
       <c r="AE49" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260211045110_not_flex_std_el_2_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>192276175.1661619</v>
+      </c>
+      <c r="B50" t="n">
+        <v>13745152.54522251</v>
+      </c>
+      <c r="C50" t="n">
+        <v>5951746.544758905</v>
+      </c>
+      <c r="D50" t="n">
+        <v>9276606.515804365</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>23021759.06102688</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5951746.544758905</v>
+      </c>
+      <c r="H50" t="n">
+        <v>154190284.9854973</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>9112384.574878754</v>
+      </c>
+      <c r="M50" t="n">
+        <v>192276175.1661619</v>
+      </c>
+      <c r="N50" t="n">
+        <v>60756.06478762717</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>60756.06478762717</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>60749.23049918144</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>6.834288431157916</v>
+      </c>
+      <c r="V50" t="n">
+        <v>388.1740000247955</v>
+      </c>
+      <c r="W50" t="n">
+        <v>188445150.0217652</v>
+      </c>
+      <c r="X50" t="n">
+        <v>192276175.1661619</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>3831025.144396633</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>mea_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260211184644_mea_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>79087021.68483756</v>
+      </c>
+      <c r="B51" t="n">
+        <v>17754619.87837266</v>
+      </c>
+      <c r="C51" t="n">
+        <v>5750018.57135666</v>
+      </c>
+      <c r="D51" t="n">
+        <v>46592447.39263033</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>64347067.27100299</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5750018.57135666</v>
+      </c>
+      <c r="H51" t="n">
+        <v>7900825.757247874</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1089110.085230034</v>
+      </c>
+      <c r="M51" t="n">
+        <v>79087021.68483756</v>
+      </c>
+      <c r="N51" t="n">
+        <v>7268.969672063689</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>7268.969672063689</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>7260.733901533685</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>8.235770529824572</v>
+      </c>
+      <c r="V51" t="n">
+        <v>163.0710000991821</v>
+      </c>
+      <c r="W51" t="n">
+        <v>77615535.88661648</v>
+      </c>
+      <c r="X51" t="n">
+        <v>79087021.68483756</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1471485.798221081</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>hybrid_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260211185601_hybrid_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>79087021.68483675</v>
+      </c>
+      <c r="B52" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C52" t="n">
+        <v>5750018.57135656</v>
+      </c>
+      <c r="D52" t="n">
+        <v>46592447.39262983</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>64347067.27100232</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5750018.57135656</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7900825.75724783</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1089110.085230016</v>
+      </c>
+      <c r="M52" t="n">
+        <v>79087021.68483675</v>
+      </c>
+      <c r="N52" t="n">
+        <v>7268.969672063497</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>7268.969672063497</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>7260.733901533562</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>8.235770529824348</v>
+      </c>
+      <c r="V52" t="n">
+        <v>127.7049999237061</v>
+      </c>
+      <c r="W52" t="n">
+        <v>77797587.563115</v>
+      </c>
+      <c r="X52" t="n">
+        <v>79087021.68483675</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1289434.121721745</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>both_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260211190137_both_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>85853700.05939128</v>
+      </c>
+      <c r="B53" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C53" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D53" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G53" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H53" t="n">
+        <v>7639232.897976921</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1089110.085230011</v>
+      </c>
+      <c r="M53" t="n">
+        <v>85853700.05939128</v>
+      </c>
+      <c r="N53" t="n">
+        <v>7268.969672063541</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>7268.969672063541</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>7260.73390153353</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V53" t="n">
+        <v>16.68400001525879</v>
+      </c>
+      <c r="W53" t="n">
+        <v>85853700.05938458</v>
+      </c>
+      <c r="X53" t="n">
+        <v>85853700.05939128</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>6.690621376037598e-06</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>not_flex_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260211190712_not_flex_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>192276175.1661619</v>
+      </c>
+      <c r="B54" t="n">
+        <v>13745152.54522251</v>
+      </c>
+      <c r="C54" t="n">
+        <v>5951746.544758905</v>
+      </c>
+      <c r="D54" t="n">
+        <v>9276606.515804365</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>23021759.06102688</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5951746.544758905</v>
+      </c>
+      <c r="H54" t="n">
+        <v>154190284.9854973</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>9112384.574878754</v>
+      </c>
+      <c r="M54" t="n">
+        <v>192276175.1661619</v>
+      </c>
+      <c r="N54" t="n">
+        <v>60756.06478762717</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>60756.06478762717</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>60749.23049918144</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>6.834288431157916</v>
+      </c>
+      <c r="V54" t="n">
+        <v>389.0629999637604</v>
+      </c>
+      <c r="W54" t="n">
+        <v>188445150.0217652</v>
+      </c>
+      <c r="X54" t="n">
+        <v>192276175.1661619</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>3831025.144396633</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>mea_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216111614_mea_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>192276175.1661619</v>
+      </c>
+      <c r="B55" t="n">
+        <v>13745152.54522251</v>
+      </c>
+      <c r="C55" t="n">
+        <v>5951746.544758905</v>
+      </c>
+      <c r="D55" t="n">
+        <v>9276606.515804365</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>23021759.06102688</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5951746.544758905</v>
+      </c>
+      <c r="H55" t="n">
+        <v>154190284.9854973</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>9112384.574878754</v>
+      </c>
+      <c r="M55" t="n">
+        <v>192276175.1661619</v>
+      </c>
+      <c r="N55" t="n">
+        <v>60756.06478762717</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>60756.06478762717</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>60749.23049918144</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>6.834288431157916</v>
+      </c>
+      <c r="V55" t="n">
+        <v>387.4659998416901</v>
+      </c>
+      <c r="W55" t="n">
+        <v>188445150.0217652</v>
+      </c>
+      <c r="X55" t="n">
+        <v>192276175.1661619</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>3831025.144396633</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>mea_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216121246_mea_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>204915622.4777328</v>
+      </c>
+      <c r="B56" t="n">
+        <v>13739798.9663392</v>
+      </c>
+      <c r="C56" t="n">
+        <v>5950072.29424291</v>
+      </c>
+      <c r="D56" t="n">
+        <v>9274023.440714542</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>23013822.40705375</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5950072.29424291</v>
+      </c>
+      <c r="H56" t="n">
+        <v>166827441.9591892</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>9124285.817246949</v>
+      </c>
+      <c r="M56" t="n">
+        <v>204915622.4777328</v>
+      </c>
+      <c r="N56" t="n">
+        <v>60835.40541163561</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>60835.40541163561</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>60828.57211497828</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>6.833296660959783</v>
+      </c>
+      <c r="V56" t="n">
+        <v>4743.469999790192</v>
+      </c>
+      <c r="W56" t="n">
+        <v>201633417.6181582</v>
+      </c>
+      <c r="X56" t="n">
+        <v>204915622.4777328</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>3282204.859574616</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>mea_std_el_1_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216122203_mea_std_el_1_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>218024105.9988228</v>
+      </c>
+      <c r="B57" t="n">
+        <v>13739798.96633978</v>
+      </c>
+      <c r="C57" t="n">
+        <v>5950072.29424309</v>
+      </c>
+      <c r="D57" t="n">
+        <v>9239851.433944732</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>22979650.40028451</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5950072.29424309</v>
+      </c>
+      <c r="H57" t="n">
+        <v>179267924.187199</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>9826459.117096173</v>
+      </c>
+      <c r="M57" t="n">
+        <v>218024105.9988228</v>
+      </c>
+      <c r="N57" t="n">
+        <v>65516.50222952801</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>65516.50222952801</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>65509.72744730783</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>6.774782219306019</v>
+      </c>
+      <c r="V57" t="n">
+        <v>4467.506999969482</v>
+      </c>
+      <c r="W57" t="n">
+        <v>214060908.1911889</v>
+      </c>
+      <c r="X57" t="n">
+        <v>218024105.9988228</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>3963197.807633877</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>mea_std_el_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216134350_mea_std_el_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>192221654.4236848</v>
+      </c>
+      <c r="B58" t="n">
+        <v>13745152.54522159</v>
+      </c>
+      <c r="C58" t="n">
+        <v>5951746.544758618</v>
+      </c>
+      <c r="D58" t="n">
+        <v>9276606.515803894</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>23021759.06102549</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5951746.544758618</v>
+      </c>
+      <c r="H58" t="n">
+        <v>154135764.243025</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>9112384.574875714</v>
+      </c>
+      <c r="M58" t="n">
+        <v>192221654.4236848</v>
+      </c>
+      <c r="N58" t="n">
+        <v>60756.06478762638</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>60756.06478762638</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>60749.23049917693</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6.834288431157407</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1317.358000040054</v>
+      </c>
+      <c r="W58" t="n">
+        <v>188380241.5342354</v>
+      </c>
+      <c r="X58" t="n">
+        <v>192221654.4236848</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>3841412.889449388</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>mea_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216150121_mea_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>201198585.6791452</v>
+      </c>
+      <c r="B59" t="n">
+        <v>13739798.96633928</v>
+      </c>
+      <c r="C59" t="n">
+        <v>5950072.294242933</v>
+      </c>
+      <c r="D59" t="n">
+        <v>9274602.62727025</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>23014401.59360953</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5950072.294242933</v>
+      </c>
+      <c r="H59" t="n">
+        <v>163121727.2164164</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>9112384.574876281</v>
+      </c>
+      <c r="M59" t="n">
+        <v>201198585.6791452</v>
+      </c>
+      <c r="N59" t="n">
+        <v>60756.06478760672</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>60756.06478760672</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>60749.23049917648</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>6.834288431157353</v>
+      </c>
+      <c r="V59" t="n">
+        <v>4710.261000156403</v>
+      </c>
+      <c r="W59" t="n">
+        <v>200833341.6377033</v>
+      </c>
+      <c r="X59" t="n">
+        <v>201198585.6791452</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>365244.041441828</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>mea_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216152610_mea_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>212092130.6392016</v>
+      </c>
+      <c r="B60" t="n">
+        <v>13750510.78958165</v>
+      </c>
+      <c r="C60" t="n">
+        <v>5953422.254316078</v>
+      </c>
+      <c r="D60" t="n">
+        <v>9278612.150646215</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>23029122.94022786</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5953422.254316078</v>
+      </c>
+      <c r="H60" t="n">
+        <v>173997200.8697812</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>9112384.574876502</v>
+      </c>
+      <c r="M60" t="n">
+        <v>212092130.6392016</v>
+      </c>
+      <c r="N60" t="n">
+        <v>60756.06478760846</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>60756.06478760846</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>60749.23049917637</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>6.834288431157346</v>
+      </c>
+      <c r="V60" t="n">
+        <v>608.0920000076294</v>
+      </c>
+      <c r="W60" t="n">
+        <v>212092099.211638</v>
+      </c>
+      <c r="X60" t="n">
+        <v>212092130.6392016</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>31.42756363749504</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>mea_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216164742_mea_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>192030426.2123032</v>
+      </c>
+      <c r="B61" t="n">
+        <v>13745152.5452215</v>
+      </c>
+      <c r="C61" t="n">
+        <v>5951746.54475859</v>
+      </c>
+      <c r="D61" t="n">
+        <v>9276606.515803834</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>23021759.06102534</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5951746.54475859</v>
+      </c>
+      <c r="H61" t="n">
+        <v>153944536.0316435</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M61" t="n">
+        <v>192030426.2123032</v>
+      </c>
+      <c r="N61" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>60749.23049917645</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>6.834288431157358</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1335.611000061035</v>
+      </c>
+      <c r="W61" t="n">
+        <v>188213051.5333815</v>
+      </c>
+      <c r="X61" t="n">
+        <v>192030426.2123032</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>3817374.6789217</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>mea_std_el_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216170103_mea_std_el_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="B62" t="n">
+        <v>13745152.43109943</v>
+      </c>
+      <c r="C62" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="D62" t="n">
+        <v>9276606.51580387</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>23021758.9469033</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="H62" t="n">
+        <v>154203969.2099019</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M62" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="N62" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>60749.23049917667</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V62" t="n">
+        <v>897.5329999923706</v>
+      </c>
+      <c r="W62" t="n">
+        <v>188449821.3575299</v>
+      </c>
+      <c r="X62" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>3840037.91890958</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>mea_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216191732_mea_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>205208984.6471018</v>
+      </c>
+      <c r="B63" t="n">
+        <v>13739798.96633913</v>
+      </c>
+      <c r="C63" t="n">
+        <v>5950072.294242889</v>
+      </c>
+      <c r="D63" t="n">
+        <v>9274023.440714702</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>23013822.40705384</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5950072.294242889</v>
+      </c>
+      <c r="H63" t="n">
+        <v>167120804.1285585</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>9124285.81724656</v>
+      </c>
+      <c r="M63" t="n">
+        <v>205208984.6471018</v>
+      </c>
+      <c r="N63" t="n">
+        <v>60835.40541163835</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>60835.40541163835</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>60828.57211497779</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>6.833296660959745</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1184.503999948502</v>
+      </c>
+      <c r="W63" t="n">
+        <v>201862338.0080402</v>
+      </c>
+      <c r="X63" t="n">
+        <v>205208984.6471018</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>3346646.63906154</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>mea_std_el_1_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216193523_mea_std_el_1_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="B64" t="n">
+        <v>13739798.96633944</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5950072.294242985</v>
+      </c>
+      <c r="D64" t="n">
+        <v>9254331.097830169</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>22994130.06416961</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5950072.294242985</v>
+      </c>
+      <c r="H64" t="n">
+        <v>177450920.713949</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>9528928.057837928</v>
+      </c>
+      <c r="M64" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="N64" t="n">
+        <v>63532.98662872728</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>63532.98662872728</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>63526.18705225232</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>6.799576474244003</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1287.038000106812</v>
+      </c>
+      <c r="W64" t="n">
+        <v>214927822.7666802</v>
+      </c>
+      <c r="X64" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>996228.3635193706</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>mea_std_el_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216195759_mea_std_el_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>191223609.8678495</v>
+      </c>
+      <c r="B65" t="n">
+        <v>13739798.96633921</v>
+      </c>
+      <c r="C65" t="n">
+        <v>5950072.294242912</v>
+      </c>
+      <c r="D65" t="n">
+        <v>9274602.627270218</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>23014401.59360943</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5950072.294242912</v>
+      </c>
+      <c r="H65" t="n">
+        <v>153146751.4051209</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>9112384.574876295</v>
+      </c>
+      <c r="M65" t="n">
+        <v>191223609.8678495</v>
+      </c>
+      <c r="N65" t="n">
+        <v>60756.06478760666</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>60756.06478760666</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>60749.23049917628</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>6.834288431157314</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1085.830000162125</v>
+      </c>
+      <c r="W65" t="n">
+        <v>188417490.5511152</v>
+      </c>
+      <c r="X65" t="n">
+        <v>191223609.8678495</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2806119.316734314</v>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>mea_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216202224_mea_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>204458807.1498318</v>
+      </c>
+      <c r="B66" t="n">
+        <v>13741582.97462855</v>
+      </c>
+      <c r="C66" t="n">
+        <v>5950630.215750016</v>
+      </c>
+      <c r="D66" t="n">
+        <v>9271794.772517361</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>23013377.74714591</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5950630.215750016</v>
+      </c>
+      <c r="H66" t="n">
+        <v>166310996.7939111</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>9183802.393024839</v>
+      </c>
+      <c r="M66" t="n">
+        <v>204458807.1498318</v>
+      </c>
+      <c r="N66" t="n">
+        <v>61232.17762378007</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>61232.17762378007</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>61225.34928683309</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>6.828336946311606</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1569.171999931335</v>
+      </c>
+      <c r="W66" t="n">
+        <v>201572764.2759136</v>
+      </c>
+      <c r="X66" t="n">
+        <v>204458807.1498318</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>2886042.873918265</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>mea_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216204314_mea_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>217532591.2913606</v>
+      </c>
+      <c r="B67" t="n">
+        <v>13745152.43109941</v>
+      </c>
+      <c r="C67" t="n">
+        <v>5951746.544758595</v>
+      </c>
+      <c r="D67" t="n">
+        <v>9114363.647776082</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>22859516.07887549</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5951746.544758595</v>
+      </c>
+      <c r="H67" t="n">
+        <v>176275144.8581391</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>12446183.80958737</v>
+      </c>
+      <c r="M67" t="n">
+        <v>217532591.2913606</v>
+      </c>
+      <c r="N67" t="n">
+        <v>82981.11520241045</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>82981.11520241045</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>82974.5587305826</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>6.556471828264787</v>
+      </c>
+      <c r="V67" t="n">
+        <v>891.8500001430511</v>
+      </c>
+      <c r="W67" t="n">
+        <v>213750022.7074036</v>
+      </c>
+      <c r="X67" t="n">
+        <v>217532591.2913606</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>3782568.583957046</v>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>mea_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216211213_mea_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="B68" t="n">
+        <v>13745152.43109943</v>
+      </c>
+      <c r="C68" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="D68" t="n">
+        <v>9276606.51580387</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>23021758.9469033</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="H68" t="n">
+        <v>154109690.9731993</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M68" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="N68" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>60749.23049917666</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1332.487999916077</v>
+      </c>
+      <c r="W68" t="n">
+        <v>188366125.7761273</v>
+      </c>
+      <c r="X68" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>3829455.263609529</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>mea_std_el_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216213005_mea_std_el_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>202134058.6779422</v>
+      </c>
+      <c r="B69" t="n">
+        <v>13739798.96633925</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5950072.294242918</v>
+      </c>
+      <c r="D69" t="n">
+        <v>9258964.59027354</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>22998763.55661279</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5950072.294242918</v>
+      </c>
+      <c r="H69" t="n">
+        <v>163751504.7082116</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>9433718.118874971</v>
+      </c>
+      <c r="M69" t="n">
+        <v>202134058.6779422</v>
+      </c>
+      <c r="N69" t="n">
+        <v>62898.26163646928</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>62898.26163646928</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>62891.4541258342</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>6.80751063582411</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1026.434000015259</v>
+      </c>
+      <c r="W69" t="n">
+        <v>201007861.5404932</v>
+      </c>
+      <c r="X69" t="n">
+        <v>202134058.6779422</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1126197.137449086</v>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>mea_std_el_2_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216215529_mea_std_el_2_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>212747892.4667212</v>
+      </c>
+      <c r="B70" t="n">
+        <v>13748724.18937087</v>
+      </c>
+      <c r="C70" t="n">
+        <v>5952863.522230087</v>
+      </c>
+      <c r="D70" t="n">
+        <v>9110436.956984576</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>22859161.14635545</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5952863.522230087</v>
+      </c>
+      <c r="H70" t="n">
+        <v>171381526.7493628</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>12554341.04877292</v>
+      </c>
+      <c r="M70" t="n">
+        <v>212747892.4667212</v>
+      </c>
+      <c r="N70" t="n">
+        <v>83702.1544505106</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>83702.1544505106</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>83695.60699182161</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>6.547458724999242</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1336.561000108719</v>
+      </c>
+      <c r="W70" t="n">
+        <v>212065267.803628</v>
+      </c>
+      <c r="X70" t="n">
+        <v>212747892.4667212</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>682624.6630932391</v>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>mea_std_el_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216221449_mea_std_el_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="B71" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C71" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D71" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H71" t="n">
+        <v>154203969.2099126</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M71" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="N71" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V71" t="n">
+        <v>4.467000007629395</v>
+      </c>
+      <c r="W71" t="n">
+        <v>188450457.7877902</v>
+      </c>
+      <c r="X71" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>3839401.48866114</v>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216224029_mea_inflex_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>205216527.8788469</v>
+      </c>
+      <c r="B72" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C72" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D72" t="n">
+        <v>9276027.076989908</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>23021179.50808933</v>
+      </c>
+      <c r="G72" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H72" t="n">
+        <v>167119310.8252844</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>9124291.000714663</v>
+      </c>
+      <c r="M72" t="n">
+        <v>205216527.8788469</v>
+      </c>
+      <c r="N72" t="n">
+        <v>60835.43996765997</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>60835.43996765997</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>60828.60667143137</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>6.833296229004177</v>
+      </c>
+      <c r="V72" t="n">
+        <v>3.676000118255615</v>
+      </c>
+      <c r="W72" t="n">
+        <v>201112915.2994929</v>
+      </c>
+      <c r="X72" t="n">
+        <v>205216527.8788469</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>4103612.579354048</v>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_el_1_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216224246_mea_inflex_std_el_1_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="B73" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C73" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9241840.186941134</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>22986992.61804055</v>
+      </c>
+      <c r="G73" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H73" t="n">
+        <v>179275409.5395269</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>9826770.125171607</v>
+      </c>
+      <c r="M73" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="N73" t="n">
+        <v>65518.57559077922</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>65518.57559077922</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>65511.80083447765</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>6.774756301966099</v>
+      </c>
+      <c r="V73" t="n">
+        <v>3.587999820709229</v>
+      </c>
+      <c r="W73" t="n">
+        <v>213804443.9785298</v>
+      </c>
+      <c r="X73" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>4236474.84896794</v>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_el_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216224625_mea_inflex_std_el_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>192242720.1581005</v>
+      </c>
+      <c r="B74" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C74" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D74" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G74" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H74" t="n">
+        <v>154156830.0915617</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M74" t="n">
+        <v>192242720.1581005</v>
+      </c>
+      <c r="N74" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V74" t="n">
+        <v>4.553999900817871</v>
+      </c>
+      <c r="W74" t="n">
+        <v>188400111.2845754</v>
+      </c>
+      <c r="X74" t="n">
+        <v>192242720.1581005</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>3842608.873525053</v>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216224841_mea_inflex_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>205089641.4985768</v>
+      </c>
+      <c r="B75" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C75" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9266756.055959731</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23011908.48705915</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H75" t="n">
+        <v>166811192.6526323</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>9314793.814126715</v>
+      </c>
+      <c r="M75" t="n">
+        <v>205089641.4985768</v>
+      </c>
+      <c r="N75" t="n">
+        <v>62105.44284850587</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>62105.44284850587</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>62098.62542751172</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>6.817420994553173</v>
+      </c>
+      <c r="V75" t="n">
+        <v>3.684000015258789</v>
+      </c>
+      <c r="W75" t="n">
+        <v>200992936.5307681</v>
+      </c>
+      <c r="X75" t="n">
+        <v>205089641.4985768</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4096704.967808664</v>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216225058_mea_inflex_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>217532591.2913601</v>
+      </c>
+      <c r="B76" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C76" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D76" t="n">
+        <v>9114363.64777622</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>22859516.07887564</v>
+      </c>
+      <c r="G76" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H76" t="n">
+        <v>176275144.8581385</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>12446183.80958737</v>
+      </c>
+      <c r="M76" t="n">
+        <v>217532591.2913601</v>
+      </c>
+      <c r="N76" t="n">
+        <v>82981.11520241042</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>82981.11520241042</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>82974.55873058242</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>6.556471828264789</v>
+      </c>
+      <c r="V76" t="n">
+        <v>3.726999998092651</v>
+      </c>
+      <c r="W76" t="n">
+        <v>213296116.4423921</v>
+      </c>
+      <c r="X76" t="n">
+        <v>217532591.2913601</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>4236474.848968029</v>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216225455_mea_inflex_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="B77" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C77" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D77" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H77" t="n">
+        <v>154109690.9732109</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M77" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="N77" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V77" t="n">
+        <v>4.694000005722046</v>
+      </c>
+      <c r="W77" t="n">
+        <v>188357250.9661896</v>
+      </c>
+      <c r="X77" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>3838330.073559999</v>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_el_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216225712_mea_inflex_std_el_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>204924298.6991124</v>
+      </c>
+      <c r="B78" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C78" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D78" t="n">
+        <v>9254587.840857625</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>22999740.27195704</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H78" t="n">
+        <v>166407983.1256667</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>9564828.756730033</v>
+      </c>
+      <c r="M78" t="n">
+        <v>204924298.6991124</v>
+      </c>
+      <c r="N78" t="n">
+        <v>63772.3216296161</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>63772.3216296161</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>63765.52504486717</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>6.79658474933623</v>
+      </c>
+      <c r="V78" t="n">
+        <v>3.782999992370605</v>
+      </c>
+      <c r="W78" t="n">
+        <v>200831073.6047956</v>
+      </c>
+      <c r="X78" t="n">
+        <v>204924298.6991124</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>4093225.094316751</v>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_el_2_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216225930_mea_inflex_std_el_2_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="B79" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C79" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D79" t="n">
+        <v>8982831.036910607</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>22727983.46801002</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H79" t="n">
+        <v>172809702.1770405</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>15148942.4748709</v>
+      </c>
+      <c r="M79" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="N79" t="n">
+        <v>100999.2810744117</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>100999.2810744117</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>100992.9498324723</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>6.331241939491165</v>
+      </c>
+      <c r="V79" t="n">
+        <v>3.880000114440918</v>
+      </c>
+      <c r="W79" t="n">
+        <v>212401899.815712</v>
+      </c>
+      <c r="X79" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>4236474.848967999</v>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_el_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216230351_mea_inflex_std_el_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79087021.68483663</v>
+      </c>
+      <c r="B80" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5750018.571356563</v>
+      </c>
+      <c r="D80" t="n">
+        <v>46592447.39262985</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>64347067.27100235</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5750018.571356563</v>
+      </c>
+      <c r="H80" t="n">
+        <v>7900825.757247684</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1089110.08523002</v>
+      </c>
+      <c r="M80" t="n">
+        <v>79087021.68483663</v>
+      </c>
+      <c r="N80" t="n">
+        <v>7268.969672063523</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>7268.969672063523</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>7260.733901533587</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V80" t="n">
+        <v>815.3149998188019</v>
+      </c>
+      <c r="W80" t="n">
+        <v>77796638.57871668</v>
+      </c>
+      <c r="X80" t="n">
+        <v>79087021.68483663</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1290383.106119946</v>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>hybrid_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216230606_hybrid_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>84991605.48530889</v>
+      </c>
+      <c r="B81" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C81" t="n">
+        <v>5750018.571356562</v>
+      </c>
+      <c r="D81" t="n">
+        <v>46592447.39262984</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>64347067.27100233</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5750018.571356562</v>
+      </c>
+      <c r="H81" t="n">
+        <v>13805409.55771997</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1089110.085230019</v>
+      </c>
+      <c r="M81" t="n">
+        <v>84991605.48530889</v>
+      </c>
+      <c r="N81" t="n">
+        <v>7268.969672063508</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>7268.969672063508</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>7260.733901533585</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V81" t="n">
+        <v>199.6280000209808</v>
+      </c>
+      <c r="W81" t="n">
+        <v>83902811.7232549</v>
+      </c>
+      <c r="X81" t="n">
+        <v>84991605.48530889</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>1088793.762053981</v>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>hybrid_std_el_1_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216232158_hybrid_std_el_1_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>90896189.28578112</v>
+      </c>
+      <c r="B82" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C82" t="n">
+        <v>5750018.571356564</v>
+      </c>
+      <c r="D82" t="n">
+        <v>46592447.39262985</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>64347067.27100234</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5750018.571356564</v>
+      </c>
+      <c r="H82" t="n">
+        <v>19709993.35819219</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1089110.085230016</v>
+      </c>
+      <c r="M82" t="n">
+        <v>90896189.28578112</v>
+      </c>
+      <c r="N82" t="n">
+        <v>7268.969672063497</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>7268.969672063497</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>7260.733901533562</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V82" t="n">
+        <v>237.5450000762939</v>
+      </c>
+      <c r="W82" t="n">
+        <v>89108296.26629464</v>
+      </c>
+      <c r="X82" t="n">
+        <v>90896189.28578112</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>1787893.019486472</v>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>hybrid_std_el_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216232734_hybrid_std_el_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>79087021.68483652</v>
+      </c>
+      <c r="B83" t="n">
+        <v>17754619.87837248</v>
+      </c>
+      <c r="C83" t="n">
+        <v>5750018.571356554</v>
+      </c>
+      <c r="D83" t="n">
+        <v>46592447.3926298</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>64347067.27100228</v>
+      </c>
+      <c r="G83" t="n">
+        <v>5750018.571356554</v>
+      </c>
+      <c r="H83" t="n">
+        <v>7900825.757247675</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1089110.085230015</v>
+      </c>
+      <c r="M83" t="n">
+        <v>79087021.68483652</v>
+      </c>
+      <c r="N83" t="n">
+        <v>7268.969672063491</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>7268.969672063491</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>7260.733901533559</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>8.235770529824334</v>
+      </c>
+      <c r="V83" t="n">
+        <v>564.5880000591278</v>
+      </c>
+      <c r="W83" t="n">
+        <v>77800949.92232282</v>
+      </c>
+      <c r="X83" t="n">
+        <v>79087021.68483652</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>1286071.762513697</v>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>hybrid_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216233623_hybrid_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>84991605.4853093</v>
+      </c>
+      <c r="B84" t="n">
+        <v>17754619.87837254</v>
+      </c>
+      <c r="C84" t="n">
+        <v>5750018.571356591</v>
+      </c>
+      <c r="D84" t="n">
+        <v>46592447.39263003</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>64347067.27100257</v>
+      </c>
+      <c r="G84" t="n">
+        <v>5750018.571356591</v>
+      </c>
+      <c r="H84" t="n">
+        <v>13805409.55772009</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1089110.085230047</v>
+      </c>
+      <c r="M84" t="n">
+        <v>84991605.4853093</v>
+      </c>
+      <c r="N84" t="n">
+        <v>7268.969672063705</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>7268.969672063705</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>7260.733901533771</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>8.23577052982443</v>
+      </c>
+      <c r="V84" t="n">
+        <v>751.6909999847412</v>
+      </c>
+      <c r="W84" t="n">
+        <v>83699373.49041252</v>
+      </c>
+      <c r="X84" t="n">
+        <v>84991605.4853093</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1292231.994896784</v>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>hybrid_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260216234807_hybrid_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>90896189.28578153</v>
+      </c>
+      <c r="B85" t="n">
+        <v>17754619.87837255</v>
+      </c>
+      <c r="C85" t="n">
+        <v>5750018.571356594</v>
+      </c>
+      <c r="D85" t="n">
+        <v>46592447.39263003</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>64347067.27100258</v>
+      </c>
+      <c r="G85" t="n">
+        <v>5750018.571356594</v>
+      </c>
+      <c r="H85" t="n">
+        <v>19709993.35819235</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1089110.085230016</v>
+      </c>
+      <c r="M85" t="n">
+        <v>90896189.28578153</v>
+      </c>
+      <c r="N85" t="n">
+        <v>7268.969672063497</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>7268.969672063497</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>7260.733901533562</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>8.235770529824425</v>
+      </c>
+      <c r="V85" t="n">
+        <v>434.2690000534058</v>
+      </c>
+      <c r="W85" t="n">
+        <v>89083570.5620915</v>
+      </c>
+      <c r="X85" t="n">
+        <v>90896189.28578153</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1812618.723690033</v>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>hybrid_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217000257_hybrid_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>79087021.68483761</v>
+      </c>
+      <c r="B86" t="n">
+        <v>17754619.87837267</v>
+      </c>
+      <c r="C86" t="n">
+        <v>5750018.571356662</v>
+      </c>
+      <c r="D86" t="n">
+        <v>46592447.39263035</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>64347067.27100302</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5750018.571356662</v>
+      </c>
+      <c r="H86" t="n">
+        <v>7900825.757247874</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1089110.085230034</v>
+      </c>
+      <c r="M86" t="n">
+        <v>79087021.68483761</v>
+      </c>
+      <c r="N86" t="n">
+        <v>7268.969672063695</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>7268.969672063695</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>7260.733901533697</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>8.235770529824579</v>
+      </c>
+      <c r="V86" t="n">
+        <v>246.6860001087189</v>
+      </c>
+      <c r="W86" t="n">
+        <v>77798005.58215375</v>
+      </c>
+      <c r="X86" t="n">
+        <v>79087021.68483761</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1289016.102683857</v>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>hybrid_std_el_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217001232_hybrid_std_el_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>84991605.4853093</v>
+      </c>
+      <c r="B87" t="n">
+        <v>17754619.87837255</v>
+      </c>
+      <c r="C87" t="n">
+        <v>5750018.571356595</v>
+      </c>
+      <c r="D87" t="n">
+        <v>46592447.39263004</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>64347067.27100259</v>
+      </c>
+      <c r="G87" t="n">
+        <v>5750018.571356595</v>
+      </c>
+      <c r="H87" t="n">
+        <v>13805409.55772009</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1089110.085230021</v>
+      </c>
+      <c r="M87" t="n">
+        <v>84991605.4853093</v>
+      </c>
+      <c r="N87" t="n">
+        <v>7268.969672063537</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>7268.969672063537</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>7260.733901533601</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>8.235770529824428</v>
+      </c>
+      <c r="V87" t="n">
+        <v>755.1180000305176</v>
+      </c>
+      <c r="W87" t="n">
+        <v>83684849.32874182</v>
+      </c>
+      <c r="X87" t="n">
+        <v>84991605.4853093</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>1306756.156567484</v>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>hybrid_std_el_2_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217002211_hybrid_std_el_2_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>90896189.2857811</v>
+      </c>
+      <c r="B88" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C88" t="n">
+        <v>5750018.57135657</v>
+      </c>
+      <c r="D88" t="n">
+        <v>46592447.39262985</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>64347067.27100235</v>
+      </c>
+      <c r="G88" t="n">
+        <v>5750018.57135657</v>
+      </c>
+      <c r="H88" t="n">
+        <v>19709993.35819217</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1089110.085230015</v>
+      </c>
+      <c r="M88" t="n">
+        <v>90896189.2857811</v>
+      </c>
+      <c r="N88" t="n">
+        <v>7268.969672063477</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>7268.969672063477</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>7260.733901533544</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V88" t="n">
+        <v>601.6849999427795</v>
+      </c>
+      <c r="W88" t="n">
+        <v>89552169.19594738</v>
+      </c>
+      <c r="X88" t="n">
+        <v>90896189.2857811</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1344020.089833722</v>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>hybrid_std_el_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217003707_hybrid_std_el_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>85853700.05939652</v>
+      </c>
+      <c r="B89" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C89" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D89" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H89" t="n">
+        <v>7639232.897977064</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1089110.0852351</v>
+      </c>
+      <c r="M89" t="n">
+        <v>85853700.05939652</v>
+      </c>
+      <c r="N89" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V89" t="n">
+        <v>4.803000211715698</v>
+      </c>
+      <c r="W89" t="n">
+        <v>85853700.05943796</v>
+      </c>
+      <c r="X89" t="n">
+        <v>85853700.05939652</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>-4.144012928009033e-05</v>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217004929_hybrid_inflex_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>91496691.00059804</v>
+      </c>
+      <c r="B90" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C90" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D90" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G90" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H90" t="n">
+        <v>13282223.83917859</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1089110.0852351</v>
+      </c>
+      <c r="M90" t="n">
+        <v>91496691.00059804</v>
+      </c>
+      <c r="N90" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V90" t="n">
+        <v>4.683000087738037</v>
+      </c>
+      <c r="W90" t="n">
+        <v>91496691.00064003</v>
+      </c>
+      <c r="X90" t="n">
+        <v>91496691.00059804</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>-4.19914722442627e-05</v>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_el_1_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217005150_hybrid_inflex_std_el_1_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>99047057.3888889</v>
+      </c>
+      <c r="B91" t="n">
+        <v>14472894.50199523</v>
+      </c>
+      <c r="C91" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D91" t="n">
+        <v>40601255.16884278</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>55074149.67083801</v>
+      </c>
+      <c r="G91" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H91" t="n">
+        <v>16420683.74014716</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M91" t="n">
+        <v>99047057.3888889</v>
+      </c>
+      <c r="N91" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V91" t="n">
+        <v>4.24399995803833</v>
+      </c>
+      <c r="W91" t="n">
+        <v>97139681.94184096</v>
+      </c>
+      <c r="X91" t="n">
+        <v>99047057.38888848</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1907375.447047517</v>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_el_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217005410_hybrid_inflex_std_el_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>85833122.04299518</v>
+      </c>
+      <c r="B92" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C92" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D92" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H92" t="n">
+        <v>7618654.881575737</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1089110.0852351</v>
+      </c>
+      <c r="M92" t="n">
+        <v>85833122.04299518</v>
+      </c>
+      <c r="N92" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V92" t="n">
+        <v>4.271999835968018</v>
+      </c>
+      <c r="W92" t="n">
+        <v>85833122.04303667</v>
+      </c>
+      <c r="X92" t="n">
+        <v>85833122.04299518</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>-4.148483276367188e-05</v>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217005631_hybrid_inflex_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91455534.96779539</v>
+      </c>
+      <c r="B93" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C93" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D93" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G93" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H93" t="n">
+        <v>13241067.80637594</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1089110.0852351</v>
+      </c>
+      <c r="M93" t="n">
+        <v>91455534.96779539</v>
+      </c>
+      <c r="N93" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V93" t="n">
+        <v>4.501999855041504</v>
+      </c>
+      <c r="W93" t="n">
+        <v>91455534.96783826</v>
+      </c>
+      <c r="X93" t="n">
+        <v>91455534.96779539</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>-4.287064075469971e-05</v>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217010244_hybrid_inflex_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>98994456.48934941</v>
+      </c>
+      <c r="B94" t="n">
+        <v>14472894.50199523</v>
+      </c>
+      <c r="C94" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D94" t="n">
+        <v>40601255.16884278</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>55074149.67083801</v>
+      </c>
+      <c r="G94" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H94" t="n">
+        <v>16368082.84060809</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M94" t="n">
+        <v>98994456.48934941</v>
+      </c>
+      <c r="N94" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V94" t="n">
+        <v>4.393999814987183</v>
+      </c>
+      <c r="W94" t="n">
+        <v>97077947.89263675</v>
+      </c>
+      <c r="X94" t="n">
+        <v>98994456.48934941</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>1916508.596712664</v>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217010504_hybrid_inflex_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>85812544.02659388</v>
+      </c>
+      <c r="B95" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C95" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D95" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G95" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H95" t="n">
+        <v>7598076.865174433</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1089110.0852351</v>
+      </c>
+      <c r="M95" t="n">
+        <v>85812544.02659388</v>
+      </c>
+      <c r="N95" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V95" t="n">
+        <v>4.359999895095825</v>
+      </c>
+      <c r="W95" t="n">
+        <v>85812544.02663568</v>
+      </c>
+      <c r="X95" t="n">
+        <v>85812544.02659388</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>-4.179775714874268e-05</v>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_el_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217010722_hybrid_inflex_std_el_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>91414378.93499278</v>
+      </c>
+      <c r="B96" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C96" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D96" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G96" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H96" t="n">
+        <v>13199911.77357333</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1089110.0852351</v>
+      </c>
+      <c r="M96" t="n">
+        <v>91414378.93499278</v>
+      </c>
+      <c r="N96" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V96" t="n">
+        <v>4.464999914169312</v>
+      </c>
+      <c r="W96" t="n">
+        <v>91414378.93503517</v>
+      </c>
+      <c r="X96" t="n">
+        <v>91414378.93499278</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>-4.239380359649658e-05</v>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_el_2_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217010939_hybrid_inflex_std_el_2_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>98941855.58981031</v>
+      </c>
+      <c r="B97" t="n">
+        <v>14472894.50199523</v>
+      </c>
+      <c r="C97" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D97" t="n">
+        <v>40601255.16884278</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>55074149.67083801</v>
+      </c>
+      <c r="G97" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H97" t="n">
+        <v>16315481.94106899</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M97" t="n">
+        <v>98941855.58981031</v>
+      </c>
+      <c r="N97" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V97" t="n">
+        <v>4.513000011444092</v>
+      </c>
+      <c r="W97" t="n">
+        <v>97016213.84343323</v>
+      </c>
+      <c r="X97" t="n">
+        <v>98941855.58981031</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>1925641.746377081</v>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_el_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217011200_hybrid_inflex_std_el_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>79087021.68483682</v>
+      </c>
+      <c r="B98" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C98" t="n">
+        <v>5750018.571356567</v>
+      </c>
+      <c r="D98" t="n">
+        <v>46592447.39262986</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>64347067.27100235</v>
+      </c>
+      <c r="G98" t="n">
+        <v>5750018.571356567</v>
+      </c>
+      <c r="H98" t="n">
+        <v>7900825.757247848</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1089110.085230055</v>
+      </c>
+      <c r="M98" t="n">
+        <v>79087021.68483682</v>
+      </c>
+      <c r="N98" t="n">
+        <v>7268.969672063748</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>7268.969672063748</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>7260.733901533817</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>8.235770529824373</v>
+      </c>
+      <c r="V98" t="n">
+        <v>331.3940000534058</v>
+      </c>
+      <c r="W98" t="n">
+        <v>77796004.20183882</v>
+      </c>
+      <c r="X98" t="n">
+        <v>79087021.68483682</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>1291017.482997999</v>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>both_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217011438_both_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>84991605.4853089</v>
+      </c>
+      <c r="B99" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C99" t="n">
+        <v>5750018.571356565</v>
+      </c>
+      <c r="D99" t="n">
+        <v>46592447.39262986</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>64347067.27100235</v>
+      </c>
+      <c r="G99" t="n">
+        <v>5750018.571356565</v>
+      </c>
+      <c r="H99" t="n">
+        <v>13805409.55771993</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1089110.085230054</v>
+      </c>
+      <c r="M99" t="n">
+        <v>84991605.4853089</v>
+      </c>
+      <c r="N99" t="n">
+        <v>7268.969672063741</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>7268.969672063741</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>7260.733901533811</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>8.235770529824372</v>
+      </c>
+      <c r="V99" t="n">
+        <v>423.4119999408722</v>
+      </c>
+      <c r="W99" t="n">
+        <v>83700588.00231151</v>
+      </c>
+      <c r="X99" t="n">
+        <v>84991605.4853089</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>1291017.482997388</v>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>both_std_el_1_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217012308_both_std_el_1_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>90896189.28578062</v>
+      </c>
+      <c r="B100" t="n">
+        <v>17754619.87837244</v>
+      </c>
+      <c r="C100" t="n">
+        <v>5750018.571356532</v>
+      </c>
+      <c r="D100" t="n">
+        <v>46592447.39262971</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>64347067.27100215</v>
+      </c>
+      <c r="G100" t="n">
+        <v>5750018.571356532</v>
+      </c>
+      <c r="H100" t="n">
+        <v>19709993.35819193</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1089110.085230016</v>
+      </c>
+      <c r="M100" t="n">
+        <v>90896189.28578062</v>
+      </c>
+      <c r="N100" t="n">
+        <v>7268.969672063497</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>7268.969672063497</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>7260.733901533562</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>8.235770529824286</v>
+      </c>
+      <c r="V100" t="n">
+        <v>1741.542999982834</v>
+      </c>
+      <c r="W100" t="n">
+        <v>89604908.8998688</v>
+      </c>
+      <c r="X100" t="n">
+        <v>90896189.28578062</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1291280.385911822</v>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>both_std_el_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217013800_both_std_el_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>79087021.68483679</v>
+      </c>
+      <c r="B101" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C101" t="n">
+        <v>5750018.57135656</v>
+      </c>
+      <c r="D101" t="n">
+        <v>46592447.39262985</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>64347067.27100235</v>
+      </c>
+      <c r="G101" t="n">
+        <v>5750018.57135656</v>
+      </c>
+      <c r="H101" t="n">
+        <v>7900825.757247839</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1089110.08523004</v>
+      </c>
+      <c r="M101" t="n">
+        <v>79087021.68483679</v>
+      </c>
+      <c r="N101" t="n">
+        <v>7268.969672063633</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>7268.969672063633</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>7260.733901533712</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>8.235770529824363</v>
+      </c>
+      <c r="V101" t="n">
+        <v>324.3239998817444</v>
+      </c>
+      <c r="W101" t="n">
+        <v>77796004.20183899</v>
+      </c>
+      <c r="X101" t="n">
+        <v>79087021.68483679</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>1291017.482997805</v>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>both_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217021001_both_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>84991605.48530883</v>
+      </c>
+      <c r="B102" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C102" t="n">
+        <v>5750018.571356557</v>
+      </c>
+      <c r="D102" t="n">
+        <v>46592447.39262985</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>64347067.27100235</v>
+      </c>
+      <c r="G102" t="n">
+        <v>5750018.571356557</v>
+      </c>
+      <c r="H102" t="n">
+        <v>13805409.55771989</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1089110.085230023</v>
+      </c>
+      <c r="M102" t="n">
+        <v>84991605.48530883</v>
+      </c>
+      <c r="N102" t="n">
+        <v>7268.969672063503</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>7268.969672063503</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>7260.733901533587</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V102" t="n">
+        <v>627.7460000514984</v>
+      </c>
+      <c r="W102" t="n">
+        <v>83699373.4904128</v>
+      </c>
+      <c r="X102" t="n">
+        <v>84991605.48530883</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>1292231.994896024</v>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>both_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217021825_both_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>90896189.28578101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C103" t="n">
+        <v>5750018.571356568</v>
+      </c>
+      <c r="D103" t="n">
+        <v>46592447.39262985</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>64347067.27100235</v>
+      </c>
+      <c r="G103" t="n">
+        <v>5750018.571356568</v>
+      </c>
+      <c r="H103" t="n">
+        <v>19709993.35819208</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>1089110.085230011</v>
+      </c>
+      <c r="M103" t="n">
+        <v>90896189.28578101</v>
+      </c>
+      <c r="N103" t="n">
+        <v>7268.969672063449</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>7268.969672063449</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>7260.733901533524</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V103" t="n">
+        <v>700.452999830246</v>
+      </c>
+      <c r="W103" t="n">
+        <v>89576191.64217706</v>
+      </c>
+      <c r="X103" t="n">
+        <v>90896189.28578101</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>1319997.643603951</v>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>both_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217023155_both_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>79087021.68483675</v>
+      </c>
+      <c r="B104" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C104" t="n">
+        <v>5750018.571356563</v>
+      </c>
+      <c r="D104" t="n">
+        <v>46592447.39262985</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>64347067.27100234</v>
+      </c>
+      <c r="G104" t="n">
+        <v>5750018.571356563</v>
+      </c>
+      <c r="H104" t="n">
+        <v>7900825.757247834</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>1089110.085230012</v>
+      </c>
+      <c r="M104" t="n">
+        <v>79087021.68483675</v>
+      </c>
+      <c r="N104" t="n">
+        <v>7268.969672063474</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>7268.969672063474</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>7260.733901533535</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>8.235770529824356</v>
+      </c>
+      <c r="V104" t="n">
+        <v>1251.295000076294</v>
+      </c>
+      <c r="W104" t="n">
+        <v>77796004.20183904</v>
+      </c>
+      <c r="X104" t="n">
+        <v>79087021.68483675</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>1291017.482997701</v>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>both_std_el_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217024635_both_std_el_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>84991605.48530889</v>
+      </c>
+      <c r="B105" t="n">
+        <v>17754619.87837249</v>
+      </c>
+      <c r="C105" t="n">
+        <v>5750018.571356565</v>
+      </c>
+      <c r="D105" t="n">
+        <v>46592447.39262985</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>64347067.27100234</v>
+      </c>
+      <c r="G105" t="n">
+        <v>5750018.571356565</v>
+      </c>
+      <c r="H105" t="n">
+        <v>13805409.55771992</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>1089110.085230057</v>
+      </c>
+      <c r="M105" t="n">
+        <v>84991605.48530889</v>
+      </c>
+      <c r="N105" t="n">
+        <v>7268.969672063754</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>7268.969672063754</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>7260.733901533835</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>8.23577052982437</v>
+      </c>
+      <c r="V105" t="n">
+        <v>1140.358000040054</v>
+      </c>
+      <c r="W105" t="n">
+        <v>83687397.57779814</v>
+      </c>
+      <c r="X105" t="n">
+        <v>84991605.48530889</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>1304207.907510743</v>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>both_std_el_2_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217031026_both_std_el_2_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>90896189.28578097</v>
+      </c>
+      <c r="B106" t="n">
+        <v>17754619.87837248</v>
+      </c>
+      <c r="C106" t="n">
+        <v>5750018.571356561</v>
+      </c>
+      <c r="D106" t="n">
+        <v>46592447.39262983</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>64347067.27100231</v>
+      </c>
+      <c r="G106" t="n">
+        <v>5750018.571356561</v>
+      </c>
+      <c r="H106" t="n">
+        <v>19709993.35819208</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1089110.08523002</v>
+      </c>
+      <c r="M106" t="n">
+        <v>90896189.28578097</v>
+      </c>
+      <c r="N106" t="n">
+        <v>7268.969672063524</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>7268.969672063524</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>7260.73390153359</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>8.235770529824347</v>
+      </c>
+      <c r="V106" t="n">
+        <v>568.194000005722</v>
+      </c>
+      <c r="W106" t="n">
+        <v>89521673.10324273</v>
+      </c>
+      <c r="X106" t="n">
+        <v>90896189.28578097</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>1374516.182538241</v>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>both_std_el_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217033226_both_std_el_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>85853700.05939128</v>
+      </c>
+      <c r="B107" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C107" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D107" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H107" t="n">
+        <v>7639232.897976921</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>1089110.085230009</v>
+      </c>
+      <c r="M107" t="n">
+        <v>85853700.05939128</v>
+      </c>
+      <c r="N107" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V107" t="n">
+        <v>448.8090000152588</v>
+      </c>
+      <c r="W107" t="n">
+        <v>85853678.3984594</v>
+      </c>
+      <c r="X107" t="n">
+        <v>85853700.05939128</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>21.6609318703413</v>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>both_inflex_std_el_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217035100_both_inflex_std_el_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>91496691.00059271</v>
+      </c>
+      <c r="B108" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C108" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D108" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G108" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H108" t="n">
+        <v>13282223.83917835</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>1089110.085230009</v>
+      </c>
+      <c r="M108" t="n">
+        <v>91496691.00059271</v>
+      </c>
+      <c r="N108" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V108" t="n">
+        <v>377.4969999790192</v>
+      </c>
+      <c r="W108" t="n">
+        <v>91496669.33966112</v>
+      </c>
+      <c r="X108" t="n">
+        <v>91496691.00059271</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>21.66093158721924</v>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>both_inflex_std_el_1_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217040126_both_inflex_std_el_1_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>97139681.94179423</v>
+      </c>
+      <c r="B109" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C109" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D109" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H109" t="n">
+        <v>18925214.78037987</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1089110.085230009</v>
+      </c>
+      <c r="M109" t="n">
+        <v>97139681.94179423</v>
+      </c>
+      <c r="N109" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V109" t="n">
+        <v>412.0499999523163</v>
+      </c>
+      <c r="W109" t="n">
+        <v>97139660.28086257</v>
+      </c>
+      <c r="X109" t="n">
+        <v>97139681.94179423</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>21.66093166172504</v>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>both_inflex_std_el_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217041037_both_inflex_std_el_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>85833122.04298995</v>
+      </c>
+      <c r="B110" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C110" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D110" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G110" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H110" t="n">
+        <v>7618654.881575607</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>1089110.085230009</v>
+      </c>
+      <c r="M110" t="n">
+        <v>85833122.04298995</v>
+      </c>
+      <c r="N110" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V110" t="n">
+        <v>493.5370001792908</v>
+      </c>
+      <c r="W110" t="n">
+        <v>85833100.38205796</v>
+      </c>
+      <c r="X110" t="n">
+        <v>85833122.04298995</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>21.66093198955059</v>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>both_inflex_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217042026_both_inflex_std_el_1.5_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>91455534.9677901</v>
+      </c>
+      <c r="B111" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C111" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D111" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G111" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H111" t="n">
+        <v>13241067.80637574</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>1089110.085230009</v>
+      </c>
+      <c r="M111" t="n">
+        <v>91455534.9677901</v>
+      </c>
+      <c r="N111" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V111" t="n">
+        <v>496.2300000190735</v>
+      </c>
+      <c r="W111" t="n">
+        <v>91455513.30685839</v>
+      </c>
+      <c r="X111" t="n">
+        <v>91455534.9677901</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>21.66093170642853</v>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>both_inflex_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217043138_both_inflex_std_el_1.5_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>97077947.89259027</v>
+      </c>
+      <c r="B112" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C112" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D112" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G112" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H112" t="n">
+        <v>18863480.73117592</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1089110.085230009</v>
+      </c>
+      <c r="M112" t="n">
+        <v>97077947.89259027</v>
+      </c>
+      <c r="N112" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V112" t="n">
+        <v>500.7769999504089</v>
+      </c>
+      <c r="W112" t="n">
+        <v>97077926.23165864</v>
+      </c>
+      <c r="X112" t="n">
+        <v>97077947.89259027</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>21.66093163192272</v>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>both_inflex_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217044256_both_inflex_std_el_1.5_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>85812544.02658865</v>
+      </c>
+      <c r="B113" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C113" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D113" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G113" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H113" t="n">
+        <v>7598076.8651743</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1089110.085230009</v>
+      </c>
+      <c r="M113" t="n">
+        <v>85812544.02658865</v>
+      </c>
+      <c r="N113" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V113" t="n">
+        <v>546.8049998283386</v>
+      </c>
+      <c r="W113" t="n">
+        <v>85812522.36565685</v>
+      </c>
+      <c r="X113" t="n">
+        <v>85812544.02658865</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>21.66093179583549</v>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>both_inflex_std_el_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217045424_both_inflex_std_el_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>91414378.93498747</v>
+      </c>
+      <c r="B114" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C114" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D114" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G114" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H114" t="n">
+        <v>13199911.77357312</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1089110.085230009</v>
+      </c>
+      <c r="M114" t="n">
+        <v>91414378.93498747</v>
+      </c>
+      <c r="N114" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V114" t="n">
+        <v>546.5680000782013</v>
+      </c>
+      <c r="W114" t="n">
+        <v>91414357.27405572</v>
+      </c>
+      <c r="X114" t="n">
+        <v>91414378.93498747</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>21.66093175113201</v>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>both_inflex_std_el_2_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217050641_both_inflex_std_el_2_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>97016213.84338634</v>
+      </c>
+      <c r="B115" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C115" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D115" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G115" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H115" t="n">
+        <v>18801746.68197198</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1089110.085230009</v>
+      </c>
+      <c r="M115" t="n">
+        <v>97016213.84338634</v>
+      </c>
+      <c r="N115" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V115" t="n">
+        <v>547.2709999084473</v>
+      </c>
+      <c r="W115" t="n">
+        <v>97016192.18245468</v>
+      </c>
+      <c r="X115" t="n">
+        <v>97016213.84338634</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>21.66093166172504</v>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>both_inflex_std_el_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217051856_both_inflex_std_el_2_el_price_150</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE115"/>
+  <dimension ref="A1:AE132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12324,6 +12324,1757 @@
       <c r="AE115" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260217051856_both_inflex_std_el_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="B116" t="n">
+        <v>13745152.43109943</v>
+      </c>
+      <c r="C116" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="D116" t="n">
+        <v>9276606.51580387</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>23021758.9469033</v>
+      </c>
+      <c r="G116" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="H116" t="n">
+        <v>154203969.2099019</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M116" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="N116" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>60749.23049917667</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V116" t="n">
+        <v>925.4289999008179</v>
+      </c>
+      <c r="W116" t="n">
+        <v>188449821.3575299</v>
+      </c>
+      <c r="X116" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>3840037.91890958</v>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260223175416_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="B117" t="n">
+        <v>13739798.96633944</v>
+      </c>
+      <c r="C117" t="n">
+        <v>5950072.294242985</v>
+      </c>
+      <c r="D117" t="n">
+        <v>9254331.097830169</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>22994130.06416961</v>
+      </c>
+      <c r="G117" t="n">
+        <v>5950072.294242985</v>
+      </c>
+      <c r="H117" t="n">
+        <v>177450920.713949</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>9528928.057837928</v>
+      </c>
+      <c r="M117" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="N117" t="n">
+        <v>63532.98662872728</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>63532.98662872728</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>63526.18705225232</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="n">
+        <v>6.799576474244003</v>
+      </c>
+      <c r="V117" t="n">
+        <v>1332.891000032425</v>
+      </c>
+      <c r="W117" t="n">
+        <v>214927822.7666802</v>
+      </c>
+      <c r="X117" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>996228.3635193706</v>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260223181241_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="B118" t="n">
+        <v>13745152.43109943</v>
+      </c>
+      <c r="C118" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="D118" t="n">
+        <v>9276606.51580387</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>23021758.9469033</v>
+      </c>
+      <c r="G118" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="H118" t="n">
+        <v>154109690.9731993</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M118" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="N118" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>60749.23049917666</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V118" t="n">
+        <v>1404.888000011444</v>
+      </c>
+      <c r="W118" t="n">
+        <v>188366125.7761273</v>
+      </c>
+      <c r="X118" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>3829455.263609529</v>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260223183739_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>212747892.4667212</v>
+      </c>
+      <c r="B119" t="n">
+        <v>13748724.18937087</v>
+      </c>
+      <c r="C119" t="n">
+        <v>5952863.522230087</v>
+      </c>
+      <c r="D119" t="n">
+        <v>9110436.956984576</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>22859161.14635545</v>
+      </c>
+      <c r="G119" t="n">
+        <v>5952863.522230087</v>
+      </c>
+      <c r="H119" t="n">
+        <v>171381526.7493628</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>12554341.04877292</v>
+      </c>
+      <c r="M119" t="n">
+        <v>212747892.4667212</v>
+      </c>
+      <c r="N119" t="n">
+        <v>83702.1544505106</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>83702.1544505106</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>83695.60699182161</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>6.547458724999242</v>
+      </c>
+      <c r="V119" t="n">
+        <v>1388.566999912262</v>
+      </c>
+      <c r="W119" t="n">
+        <v>212065267.803628</v>
+      </c>
+      <c r="X119" t="n">
+        <v>212747892.4667212</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>682624.6630932391</v>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260223190407_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="B120" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C120" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D120" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G120" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H120" t="n">
+        <v>154203969.2099126</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M120" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="N120" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V120" t="n">
+        <v>3.992000102996826</v>
+      </c>
+      <c r="W120" t="n">
+        <v>188450457.7877902</v>
+      </c>
+      <c r="X120" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>3839401.48866114</v>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260223193001_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="B121" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C121" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D121" t="n">
+        <v>9241840.186941134</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>22986992.61804055</v>
+      </c>
+      <c r="G121" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H121" t="n">
+        <v>179275409.5395269</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>9826770.125171607</v>
+      </c>
+      <c r="M121" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="N121" t="n">
+        <v>65518.57559077922</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>65518.57559077922</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>65511.80083447765</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>6.774756301966099</v>
+      </c>
+      <c r="V121" t="n">
+        <v>3.11899995803833</v>
+      </c>
+      <c r="W121" t="n">
+        <v>213804443.9785298</v>
+      </c>
+      <c r="X121" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>4236474.84896794</v>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260223193254_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="B122" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C122" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D122" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G122" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H122" t="n">
+        <v>154109690.9732109</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M122" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="N122" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V122" t="n">
+        <v>4.090999841690063</v>
+      </c>
+      <c r="W122" t="n">
+        <v>188357250.9661896</v>
+      </c>
+      <c r="X122" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>3838330.073559999</v>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260223193557_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="B123" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C123" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D123" t="n">
+        <v>8982831.036910607</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>22727983.46801002</v>
+      </c>
+      <c r="G123" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H123" t="n">
+        <v>172809702.1770405</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>15148942.4748709</v>
+      </c>
+      <c r="M123" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="N123" t="n">
+        <v>100999.2810744117</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>100999.2810744117</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>100992.9498324723</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>6.331241939491165</v>
+      </c>
+      <c r="V123" t="n">
+        <v>3.299000024795532</v>
+      </c>
+      <c r="W123" t="n">
+        <v>212401899.815712</v>
+      </c>
+      <c r="X123" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>4236474.848967999</v>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260223193914_mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>85452148.78112951</v>
+      </c>
+      <c r="B124" t="n">
+        <v>19549763.77732496</v>
+      </c>
+      <c r="C124" t="n">
+        <v>6738363.308942611</v>
+      </c>
+      <c r="D124" t="n">
+        <v>50822911.99990968</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>70372675.77723463</v>
+      </c>
+      <c r="G124" t="n">
+        <v>6738363.308942611</v>
+      </c>
+      <c r="H124" t="n">
+        <v>7251999.792125764</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1089109.902826502</v>
+      </c>
+      <c r="M124" t="n">
+        <v>85452148.78112951</v>
+      </c>
+      <c r="N124" t="n">
+        <v>7268.968456055143</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>7268.968456055143</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>7260.732685510088</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>8.235770545024335</v>
+      </c>
+      <c r="V124" t="n">
+        <v>86401.57699990273</v>
+      </c>
+      <c r="W124" t="n">
+        <v>83262534.29126668</v>
+      </c>
+      <c r="X124" t="n">
+        <v>85452148.78112951</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>2189614.489862829</v>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>maxTimeLimit</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>hybrid_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260223194126_hybrid_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>96854816.41448808</v>
+      </c>
+      <c r="B125" t="n">
+        <v>19549763.77732528</v>
+      </c>
+      <c r="C125" t="n">
+        <v>6738363.308942768</v>
+      </c>
+      <c r="D125" t="n">
+        <v>50822911.99103379</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>70372675.76835907</v>
+      </c>
+      <c r="G125" t="n">
+        <v>6738363.308942768</v>
+      </c>
+      <c r="H125" t="n">
+        <v>18654667.25195621</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1089110.08523004</v>
+      </c>
+      <c r="M125" t="n">
+        <v>96854816.41448808</v>
+      </c>
+      <c r="N125" t="n">
+        <v>7268.969672063394</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>7268.969672063394</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>7260.733901533569</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>8.23577052982437</v>
+      </c>
+      <c r="V125" t="n">
+        <v>4538.18700003624</v>
+      </c>
+      <c r="W125" t="n">
+        <v>94966092.39341362</v>
+      </c>
+      <c r="X125" t="n">
+        <v>96854816.41448808</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>1888724.021074459</v>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>hybrid_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260224194504_hybrid_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>85024704.62802342</v>
+      </c>
+      <c r="B126" t="n">
+        <v>19549763.7805266</v>
+      </c>
+      <c r="C126" t="n">
+        <v>6738363.308942753</v>
+      </c>
+      <c r="D126" t="n">
+        <v>50822911.99103374</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>70372675.77156034</v>
+      </c>
+      <c r="G126" t="n">
+        <v>6738363.308942753</v>
+      </c>
+      <c r="H126" t="n">
+        <v>6824555.462290302</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1089110.085230022</v>
+      </c>
+      <c r="M126" t="n">
+        <v>85024704.62802342</v>
+      </c>
+      <c r="N126" t="n">
+        <v>7268.969672063378</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>7268.969672063378</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>7260.733901533451</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>8.235770529824356</v>
+      </c>
+      <c r="V126" t="n">
+        <v>86401.46399998665</v>
+      </c>
+      <c r="W126" t="n">
+        <v>83234748.32682408</v>
+      </c>
+      <c r="X126" t="n">
+        <v>85024704.62802342</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1789956.301199332</v>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>maxTimeLimit</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>hybrid_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260224210300_hybrid_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>95340704.1121258</v>
+      </c>
+      <c r="B127" t="n">
+        <v>19549763.81169577</v>
+      </c>
+      <c r="C127" t="n">
+        <v>6738363.308942758</v>
+      </c>
+      <c r="D127" t="n">
+        <v>50822911.99103379</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>70372675.80272955</v>
+      </c>
+      <c r="G127" t="n">
+        <v>6738363.308942758</v>
+      </c>
+      <c r="H127" t="n">
+        <v>17140554.9152235</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1089110.08522998</v>
+      </c>
+      <c r="M127" t="n">
+        <v>95340704.1121258</v>
+      </c>
+      <c r="N127" t="n">
+        <v>7268.969672063043</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>7268.969672063043</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>7260.733901533205</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>8.235770529824368</v>
+      </c>
+      <c r="V127" t="n">
+        <v>2142.647000074387</v>
+      </c>
+      <c r="W127" t="n">
+        <v>94388167.01051934</v>
+      </c>
+      <c r="X127" t="n">
+        <v>95340704.1121258</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>952537.1016064584</v>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>hybrid_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260225210655_hybrid_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>85853700.05939652</v>
+      </c>
+      <c r="B128" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C128" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D128" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G128" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H128" t="n">
+        <v>7639232.897977064</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1089110.0852351</v>
+      </c>
+      <c r="M128" t="n">
+        <v>85853700.05939652</v>
+      </c>
+      <c r="N128" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V128" t="n">
+        <v>4.759999990463257</v>
+      </c>
+      <c r="W128" t="n">
+        <v>85853700.05943796</v>
+      </c>
+      <c r="X128" t="n">
+        <v>85853700.05939652</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>-4.144012928009033e-05</v>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260225214458_hybrid_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>99047057.3888889</v>
+      </c>
+      <c r="B129" t="n">
+        <v>14472894.50199523</v>
+      </c>
+      <c r="C129" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D129" t="n">
+        <v>40601255.16884278</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>55074149.67083801</v>
+      </c>
+      <c r="G129" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H129" t="n">
+        <v>16420683.74014716</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M129" t="n">
+        <v>99047057.3888889</v>
+      </c>
+      <c r="N129" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V129" t="n">
+        <v>4.574000120162964</v>
+      </c>
+      <c r="W129" t="n">
+        <v>97139681.94184096</v>
+      </c>
+      <c r="X129" t="n">
+        <v>99047057.38888848</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>1907375.447047517</v>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260225214719_hybrid_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>85812544.02659388</v>
+      </c>
+      <c r="B130" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C130" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D130" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G130" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H130" t="n">
+        <v>7598076.865174433</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1089110.0852351</v>
+      </c>
+      <c r="M130" t="n">
+        <v>85812544.02659388</v>
+      </c>
+      <c r="N130" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V130" t="n">
+        <v>4.613000154495239</v>
+      </c>
+      <c r="W130" t="n">
+        <v>85812544.02663568</v>
+      </c>
+      <c r="X130" t="n">
+        <v>85812544.02659388</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>-4.179775714874268e-05</v>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260225215129_hybrid_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>98941855.58981031</v>
+      </c>
+      <c r="B131" t="n">
+        <v>14472894.50199523</v>
+      </c>
+      <c r="C131" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D131" t="n">
+        <v>40601255.16884278</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>55074149.67083801</v>
+      </c>
+      <c r="G131" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H131" t="n">
+        <v>16315481.94106899</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M131" t="n">
+        <v>98941855.58981031</v>
+      </c>
+      <c r="N131" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V131" t="n">
+        <v>4.318000078201294</v>
+      </c>
+      <c r="W131" t="n">
+        <v>97016213.84343323</v>
+      </c>
+      <c r="X131" t="n">
+        <v>98941855.58981031</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>1925641.746377081</v>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>hybrid_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260225215346_hybrid_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>85452148.89000103</v>
+      </c>
+      <c r="B132" t="n">
+        <v>19549763.77732497</v>
+      </c>
+      <c r="C132" t="n">
+        <v>6738363.308942611</v>
+      </c>
+      <c r="D132" t="n">
+        <v>50822911.99408956</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>70372675.77141453</v>
+      </c>
+      <c r="G132" t="n">
+        <v>6738363.308942611</v>
+      </c>
+      <c r="H132" t="n">
+        <v>7251999.787223029</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1089110.022420854</v>
+      </c>
+      <c r="M132" t="n">
+        <v>85452148.89000103</v>
+      </c>
+      <c r="N132" t="n">
+        <v>7268.969253340661</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>7268.969253340661</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>7260.733482805758</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>8.235770535058172</v>
+      </c>
+      <c r="V132" t="n">
+        <v>50441.9319999218</v>
+      </c>
+      <c r="W132" t="n">
+        <v>83259234.81754841</v>
+      </c>
+      <c r="X132" t="n">
+        <v>85452148.89000103</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>2192914.07245262</v>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>b_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260225215606_b_std_1_el_price_50</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE132"/>
+  <dimension ref="A1:AE142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14075,6 +14075,1036 @@
       <c r="AE132" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260225215606_b_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="B133" t="n">
+        <v>13745152.43109943</v>
+      </c>
+      <c r="C133" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="D133" t="n">
+        <v>9276606.51580387</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>23021758.9469033</v>
+      </c>
+      <c r="G133" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="H133" t="n">
+        <v>154203969.2099019</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M133" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="N133" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>60749.23049917667</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V133" t="n">
+        <v>944.2920000553131</v>
+      </c>
+      <c r="W133" t="n">
+        <v>188449821.3575299</v>
+      </c>
+      <c r="X133" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>3840037.91890958</v>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226161758_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="B134" t="n">
+        <v>13739798.96633944</v>
+      </c>
+      <c r="C134" t="n">
+        <v>5950072.294242985</v>
+      </c>
+      <c r="D134" t="n">
+        <v>9254331.097830169</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>22994130.06416961</v>
+      </c>
+      <c r="G134" t="n">
+        <v>5950072.294242985</v>
+      </c>
+      <c r="H134" t="n">
+        <v>177450920.713949</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>9528928.057837928</v>
+      </c>
+      <c r="M134" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="N134" t="n">
+        <v>63532.98662872728</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>63532.98662872728</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>63526.18705225232</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>6.799576474244003</v>
+      </c>
+      <c r="V134" t="n">
+        <v>1339.361999988556</v>
+      </c>
+      <c r="W134" t="n">
+        <v>214927822.7666802</v>
+      </c>
+      <c r="X134" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>996228.3635193706</v>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226163641_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="B135" t="n">
+        <v>13745152.43109943</v>
+      </c>
+      <c r="C135" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="D135" t="n">
+        <v>9276606.51580387</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>23021758.9469033</v>
+      </c>
+      <c r="G135" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="H135" t="n">
+        <v>154109690.9731993</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M135" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="N135" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>60749.23049917666</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V135" t="n">
+        <v>1395.826999902725</v>
+      </c>
+      <c r="W135" t="n">
+        <v>188366125.7761273</v>
+      </c>
+      <c r="X135" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>3829455.263609529</v>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226170146_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>212747892.4667212</v>
+      </c>
+      <c r="B136" t="n">
+        <v>13748724.18937087</v>
+      </c>
+      <c r="C136" t="n">
+        <v>5952863.522230087</v>
+      </c>
+      <c r="D136" t="n">
+        <v>9110436.956984576</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>22859161.14635545</v>
+      </c>
+      <c r="G136" t="n">
+        <v>5952863.522230087</v>
+      </c>
+      <c r="H136" t="n">
+        <v>171381526.7493628</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>12554341.04877292</v>
+      </c>
+      <c r="M136" t="n">
+        <v>212747892.4667212</v>
+      </c>
+      <c r="N136" t="n">
+        <v>83702.1544505106</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>83702.1544505106</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>83695.60699182161</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>6.547458724999242</v>
+      </c>
+      <c r="V136" t="n">
+        <v>1404.124000072479</v>
+      </c>
+      <c r="W136" t="n">
+        <v>212065267.803628</v>
+      </c>
+      <c r="X136" t="n">
+        <v>212747892.4667212</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>682624.6630932391</v>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226172804_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="B137" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C137" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D137" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G137" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H137" t="n">
+        <v>154203969.2099126</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M137" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="N137" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V137" t="n">
+        <v>4.088000059127808</v>
+      </c>
+      <c r="W137" t="n">
+        <v>188450457.7877902</v>
+      </c>
+      <c r="X137" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>3839401.48866114</v>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226175416_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="B138" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C138" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D138" t="n">
+        <v>9241840.186941134</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>22986992.61804055</v>
+      </c>
+      <c r="G138" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H138" t="n">
+        <v>179275409.5395269</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>9826770.125171607</v>
+      </c>
+      <c r="M138" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="N138" t="n">
+        <v>65518.57559077922</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>65518.57559077922</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>65511.80083447765</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>6.774756301966099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>3.157000064849854</v>
+      </c>
+      <c r="W138" t="n">
+        <v>213804443.9785298</v>
+      </c>
+      <c r="X138" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>4236474.84896794</v>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226175710_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="B139" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C139" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D139" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G139" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H139" t="n">
+        <v>154109690.9732109</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M139" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="N139" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V139" t="n">
+        <v>4.181999921798706</v>
+      </c>
+      <c r="W139" t="n">
+        <v>188357250.9661896</v>
+      </c>
+      <c r="X139" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>3838330.073559999</v>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226180013_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="B140" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C140" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D140" t="n">
+        <v>8982831.036910607</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>22727983.46801002</v>
+      </c>
+      <c r="G140" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H140" t="n">
+        <v>172809702.1770405</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>15148942.4748709</v>
+      </c>
+      <c r="M140" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="N140" t="n">
+        <v>100999.2810744117</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>100999.2810744117</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>100992.9498324723</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>6.331241939491165</v>
+      </c>
+      <c r="V140" t="n">
+        <v>3.282999992370605</v>
+      </c>
+      <c r="W140" t="n">
+        <v>212401899.815712</v>
+      </c>
+      <c r="X140" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>4236474.848967999</v>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226180327_mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>85512061.79706813</v>
+      </c>
+      <c r="B141" t="n">
+        <v>19549763.80452469</v>
+      </c>
+      <c r="C141" t="n">
+        <v>6738363.30894271</v>
+      </c>
+      <c r="D141" t="n">
+        <v>50822911.99103343</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>70372675.79555812</v>
+      </c>
+      <c r="G141" t="n">
+        <v>6738363.30894271</v>
+      </c>
+      <c r="H141" t="n">
+        <v>7311912.607337262</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>1089110.085230036</v>
+      </c>
+      <c r="M141" t="n">
+        <v>85512061.79706813</v>
+      </c>
+      <c r="N141" t="n">
+        <v>7268.969672063385</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>7268.969672063385</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>7260.733901533476</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>8.235770529824268</v>
+      </c>
+      <c r="V141" t="n">
+        <v>2523.371999979019</v>
+      </c>
+      <c r="W141" t="n">
+        <v>83235638.97311413</v>
+      </c>
+      <c r="X141" t="n">
+        <v>85512061.79706813</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>2276422.823954001</v>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>oxy_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226180537_oxy_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>96854816.41448808</v>
+      </c>
+      <c r="B142" t="n">
+        <v>19549763.77732528</v>
+      </c>
+      <c r="C142" t="n">
+        <v>6738363.308942768</v>
+      </c>
+      <c r="D142" t="n">
+        <v>50822911.99103379</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>70372675.76835907</v>
+      </c>
+      <c r="G142" t="n">
+        <v>6738363.308942768</v>
+      </c>
+      <c r="H142" t="n">
+        <v>18654667.25195621</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1089110.08523004</v>
+      </c>
+      <c r="M142" t="n">
+        <v>96854816.41448808</v>
+      </c>
+      <c r="N142" t="n">
+        <v>7268.969672063394</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>7268.969672063394</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>7260.733901533569</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>8.23577052982437</v>
+      </c>
+      <c r="V142" t="n">
+        <v>4242.52899980545</v>
+      </c>
+      <c r="W142" t="n">
+        <v>94966092.39341362</v>
+      </c>
+      <c r="X142" t="n">
+        <v>96854816.41448808</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1888724.021074459</v>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>oxy_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226185115_oxy_std_1_el_price_150</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE142"/>
+  <dimension ref="A1:AE175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15105,6 +15105,3405 @@
       <c r="AE142" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226185115_oxy_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>85024704.62802342</v>
+      </c>
+      <c r="B143" t="n">
+        <v>19549763.7805266</v>
+      </c>
+      <c r="C143" t="n">
+        <v>6738363.308942753</v>
+      </c>
+      <c r="D143" t="n">
+        <v>50822911.99103374</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>70372675.77156034</v>
+      </c>
+      <c r="G143" t="n">
+        <v>6738363.308942753</v>
+      </c>
+      <c r="H143" t="n">
+        <v>6824555.462290302</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1089110.085230022</v>
+      </c>
+      <c r="M143" t="n">
+        <v>85024704.62802342</v>
+      </c>
+      <c r="N143" t="n">
+        <v>7268.969672063378</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>7268.969672063378</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>7260.733901533451</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>8.235770529824356</v>
+      </c>
+      <c r="V143" t="n">
+        <v>86401.30700016022</v>
+      </c>
+      <c r="W143" t="n">
+        <v>83234748.32682408</v>
+      </c>
+      <c r="X143" t="n">
+        <v>85024704.62802342</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>1789956.301199332</v>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>maxTimeLimit</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>oxy_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260226200412_oxy_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="B144" t="n">
+        <v>13745152.43109943</v>
+      </c>
+      <c r="C144" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="D144" t="n">
+        <v>9276606.51580387</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>23021758.9469033</v>
+      </c>
+      <c r="G144" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="H144" t="n">
+        <v>154203969.2099019</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M144" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="N144" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>60749.23049917667</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V144" t="n">
+        <v>872.5749998092651</v>
+      </c>
+      <c r="W144" t="n">
+        <v>188449821.3575299</v>
+      </c>
+      <c r="X144" t="n">
+        <v>192289859.2764395</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>3840037.91890958</v>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227202221_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="B145" t="n">
+        <v>13739798.96633944</v>
+      </c>
+      <c r="C145" t="n">
+        <v>5950072.294242985</v>
+      </c>
+      <c r="D145" t="n">
+        <v>9254331.097830169</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>22994130.06416961</v>
+      </c>
+      <c r="G145" t="n">
+        <v>5950072.294242985</v>
+      </c>
+      <c r="H145" t="n">
+        <v>177450920.713949</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>9528928.057837928</v>
+      </c>
+      <c r="M145" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="N145" t="n">
+        <v>63532.98662872728</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>63532.98662872728</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>63526.18705225232</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="n">
+        <v>6.799576474244003</v>
+      </c>
+      <c r="V145" t="n">
+        <v>1318.231000185013</v>
+      </c>
+      <c r="W145" t="n">
+        <v>214927822.7666802</v>
+      </c>
+      <c r="X145" t="n">
+        <v>215924051.1301995</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>996228.3635193706</v>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227203954_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="B146" t="n">
+        <v>13745152.43109943</v>
+      </c>
+      <c r="C146" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="D146" t="n">
+        <v>9276606.51580387</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>23021758.9469033</v>
+      </c>
+      <c r="G146" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="H146" t="n">
+        <v>154109690.9731993</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M146" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="N146" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>60749.23049917666</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V146" t="n">
+        <v>1375.892999887466</v>
+      </c>
+      <c r="W146" t="n">
+        <v>188366125.7761273</v>
+      </c>
+      <c r="X146" t="n">
+        <v>192195581.0397369</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>3829455.263609529</v>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227210438_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>216955200.444923</v>
+      </c>
+      <c r="B147" t="n">
+        <v>13745152.43197896</v>
+      </c>
+      <c r="C147" t="n">
+        <v>5951746.545033658</v>
+      </c>
+      <c r="D147" t="n">
+        <v>8942849.759051718</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>22688002.19103068</v>
+      </c>
+      <c r="G147" t="n">
+        <v>5951746.545033658</v>
+      </c>
+      <c r="H147" t="n">
+        <v>172344965.8512446</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>15970485.85761403</v>
+      </c>
+      <c r="M147" t="n">
+        <v>216955200.444923</v>
+      </c>
+      <c r="N147" t="n">
+        <v>106476.1684974172</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>106476.1684974172</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>106469.9057174266</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="n">
+        <v>6.262779990929177</v>
+      </c>
+      <c r="V147" t="n">
+        <v>1151.644999980927</v>
+      </c>
+      <c r="W147" t="n">
+        <v>212065267.803628</v>
+      </c>
+      <c r="X147" t="n">
+        <v>216955200.444923</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>4889932.641295016</v>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227213037_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="B148" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C148" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D148" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G148" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H148" t="n">
+        <v>154203969.2099126</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M148" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="N148" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V148" t="n">
+        <v>4.010999917984009</v>
+      </c>
+      <c r="W148" t="n">
+        <v>188053384.4274834</v>
+      </c>
+      <c r="X148" t="n">
+        <v>192289859.2764513</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>4236474.848967969</v>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227215235_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="B149" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C149" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D149" t="n">
+        <v>9241840.186941134</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>22986992.61804055</v>
+      </c>
+      <c r="G149" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H149" t="n">
+        <v>179275409.5395269</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>9826770.125171607</v>
+      </c>
+      <c r="M149" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="N149" t="n">
+        <v>65518.57559077922</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>65518.57559077922</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>65511.80083447765</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="n">
+        <v>6.774756301966099</v>
+      </c>
+      <c r="V149" t="n">
+        <v>3.217999935150146</v>
+      </c>
+      <c r="W149" t="n">
+        <v>213804443.9785298</v>
+      </c>
+      <c r="X149" t="n">
+        <v>218040918.8274977</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>4236474.84896794</v>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227215529_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="B150" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C150" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D150" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G150" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H150" t="n">
+        <v>154109690.9732109</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M150" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="N150" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V150" t="n">
+        <v>4.069000005722046</v>
+      </c>
+      <c r="W150" t="n">
+        <v>187959106.1907818</v>
+      </c>
+      <c r="X150" t="n">
+        <v>192195581.0397496</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>4236474.848967761</v>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227215832_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="B151" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C151" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D151" t="n">
+        <v>8982831.036910607</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>22727983.46801002</v>
+      </c>
+      <c r="G151" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H151" t="n">
+        <v>172809702.1770405</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>15148942.4748709</v>
+      </c>
+      <c r="M151" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="N151" t="n">
+        <v>100999.2810744117</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>100999.2810744117</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>100992.9498324723</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="n">
+        <v>6.331241939491165</v>
+      </c>
+      <c r="V151" t="n">
+        <v>3.184000015258789</v>
+      </c>
+      <c r="W151" t="n">
+        <v>212401899.815712</v>
+      </c>
+      <c r="X151" t="n">
+        <v>216638374.66468</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>4236474.848967999</v>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227220149_mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>85777492.59565657</v>
+      </c>
+      <c r="B152" t="n">
+        <v>19549763.77732526</v>
+      </c>
+      <c r="C152" t="n">
+        <v>6738363.308942754</v>
+      </c>
+      <c r="D152" t="n">
+        <v>50822911.99103374</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>70372675.76835901</v>
+      </c>
+      <c r="G152" t="n">
+        <v>6738363.308942754</v>
+      </c>
+      <c r="H152" t="n">
+        <v>7577343.433124813</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1089110.085230004</v>
+      </c>
+      <c r="M152" t="n">
+        <v>85777492.59565657</v>
+      </c>
+      <c r="N152" t="n">
+        <v>7268.969672063351</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>7268.969672063351</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>7260.733901533421</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="n">
+        <v>8.235770529824357</v>
+      </c>
+      <c r="V152" t="n">
+        <v>1884.56299996376</v>
+      </c>
+      <c r="W152" t="n">
+        <v>83231040.11779669</v>
+      </c>
+      <c r="X152" t="n">
+        <v>85777492.59565657</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>2546452.477859885</v>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>oxy_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227220400_oxy_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>97054507.22979654</v>
+      </c>
+      <c r="B153" t="n">
+        <v>19549763.77732607</v>
+      </c>
+      <c r="C153" t="n">
+        <v>6738363.308943202</v>
+      </c>
+      <c r="D153" t="n">
+        <v>50822911.99103604</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>70372675.7683621</v>
+      </c>
+      <c r="G153" t="n">
+        <v>6738363.308943202</v>
+      </c>
+      <c r="H153" t="n">
+        <v>18854358.06726108</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1089110.085230156</v>
+      </c>
+      <c r="M153" t="n">
+        <v>97054507.22979654</v>
+      </c>
+      <c r="N153" t="n">
+        <v>7268.969672064162</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>7268.969672064162</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>7260.733901534255</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>8.235770529825141</v>
+      </c>
+      <c r="V153" t="n">
+        <v>1307.694000005722</v>
+      </c>
+      <c r="W153" t="n">
+        <v>94962524.92624454</v>
+      </c>
+      <c r="X153" t="n">
+        <v>97054507.22979654</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>2091982.303552002</v>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>oxy_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227223854_oxy_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>85787158.93756197</v>
+      </c>
+      <c r="B154" t="n">
+        <v>19549763.77732517</v>
+      </c>
+      <c r="C154" t="n">
+        <v>6738363.30894271</v>
+      </c>
+      <c r="D154" t="n">
+        <v>50822911.99103343</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>70372675.7683586</v>
+      </c>
+      <c r="G154" t="n">
+        <v>6738363.30894271</v>
+      </c>
+      <c r="H154" t="n">
+        <v>7587009.775030624</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1089110.085230035</v>
+      </c>
+      <c r="M154" t="n">
+        <v>85787158.93756197</v>
+      </c>
+      <c r="N154" t="n">
+        <v>7268.969672063379</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>7268.969672063379</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>7260.733901533471</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="n">
+        <v>8.235770529824267</v>
+      </c>
+      <c r="V154" t="n">
+        <v>1278.578999996185</v>
+      </c>
+      <c r="W154" t="n">
+        <v>83217888.54540576</v>
+      </c>
+      <c r="X154" t="n">
+        <v>85787158.93756197</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>2569270.392156214</v>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>oxy_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227230257_oxy_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>96966493.79340707</v>
+      </c>
+      <c r="B155" t="n">
+        <v>19549763.77732527</v>
+      </c>
+      <c r="C155" t="n">
+        <v>6738363.308942761</v>
+      </c>
+      <c r="D155" t="n">
+        <v>50822911.99103375</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>70372675.76835901</v>
+      </c>
+      <c r="G155" t="n">
+        <v>6738363.308942761</v>
+      </c>
+      <c r="H155" t="n">
+        <v>18766344.63087527</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1089110.08523004</v>
+      </c>
+      <c r="M155" t="n">
+        <v>96966493.79340707</v>
+      </c>
+      <c r="N155" t="n">
+        <v>7268.969672063394</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>7268.969672063394</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>7260.733901533563</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>8.235770529824356</v>
+      </c>
+      <c r="V155" t="n">
+        <v>1115.996000051498</v>
+      </c>
+      <c r="W155" t="n">
+        <v>94384446.24210769</v>
+      </c>
+      <c r="X155" t="n">
+        <v>96966493.79340707</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>2582047.551299378</v>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>oxy_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227232803_oxy_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>85853700.05939652</v>
+      </c>
+      <c r="B156" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C156" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D156" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G156" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H156" t="n">
+        <v>7639232.897977064</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1089110.0852351</v>
+      </c>
+      <c r="M156" t="n">
+        <v>85853700.05939652</v>
+      </c>
+      <c r="N156" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V156" t="n">
+        <v>2.940999984741211</v>
+      </c>
+      <c r="W156" t="n">
+        <v>85853700.05943796</v>
+      </c>
+      <c r="X156" t="n">
+        <v>85853700.05939652</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>-4.144012928009033e-05</v>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227234853_oxy_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>99047057.3888889</v>
+      </c>
+      <c r="B157" t="n">
+        <v>14472894.50199523</v>
+      </c>
+      <c r="C157" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D157" t="n">
+        <v>40601255.16884278</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>55074149.67083801</v>
+      </c>
+      <c r="G157" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H157" t="n">
+        <v>16420683.74014716</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M157" t="n">
+        <v>99047057.3888889</v>
+      </c>
+      <c r="N157" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V157" t="n">
+        <v>2.939000129699707</v>
+      </c>
+      <c r="W157" t="n">
+        <v>97139681.94184096</v>
+      </c>
+      <c r="X157" t="n">
+        <v>99047057.38888848</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1907375.447047517</v>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227235105_oxy_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>85812544.02659388</v>
+      </c>
+      <c r="B158" t="n">
+        <v>19553428.22612901</v>
+      </c>
+      <c r="C158" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="D158" t="n">
+        <v>50831547.95827343</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>70384976.18440245</v>
+      </c>
+      <c r="G158" t="n">
+        <v>6740380.891781891</v>
+      </c>
+      <c r="H158" t="n">
+        <v>7598076.865174433</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1089110.0852351</v>
+      </c>
+      <c r="M158" t="n">
+        <v>85812544.02659388</v>
+      </c>
+      <c r="N158" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>7268.969672063526</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>7260.733901533531</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>8.235770529824359</v>
+      </c>
+      <c r="V158" t="n">
+        <v>3.033999919891357</v>
+      </c>
+      <c r="W158" t="n">
+        <v>85812544.02663568</v>
+      </c>
+      <c r="X158" t="n">
+        <v>85812544.02659388</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>-4.179775714874268e-05</v>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227235509_oxy_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>98941855.58981031</v>
+      </c>
+      <c r="B159" t="n">
+        <v>14472894.50199523</v>
+      </c>
+      <c r="C159" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D159" t="n">
+        <v>40601255.16884278</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>55074149.67083801</v>
+      </c>
+      <c r="G159" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H159" t="n">
+        <v>16315481.94106899</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M159" t="n">
+        <v>98941855.58981031</v>
+      </c>
+      <c r="N159" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V159" t="n">
+        <v>2.916999816894531</v>
+      </c>
+      <c r="W159" t="n">
+        <v>97016213.84343323</v>
+      </c>
+      <c r="X159" t="n">
+        <v>98941855.58981031</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1925641.746377081</v>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260227235722_oxy_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>194588335.1086689</v>
+      </c>
+      <c r="B160" t="n">
+        <v>13745152.54522158</v>
+      </c>
+      <c r="C160" t="n">
+        <v>5951746.544758614</v>
+      </c>
+      <c r="D160" t="n">
+        <v>9276606.51580389</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>23021759.06102547</v>
+      </c>
+      <c r="G160" t="n">
+        <v>5951746.544758614</v>
+      </c>
+      <c r="H160" t="n">
+        <v>156502444.9280091</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>9112384.574875714</v>
+      </c>
+      <c r="M160" t="n">
+        <v>194588335.1086689</v>
+      </c>
+      <c r="N160" t="n">
+        <v>60756.06478762638</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>60756.06478762638</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>60749.23049917693</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>6.834288431157401</v>
+      </c>
+      <c r="V160" t="n">
+        <v>1927.151000022888</v>
+      </c>
+      <c r="W160" t="n">
+        <v>190317612.7668511</v>
+      </c>
+      <c r="X160" t="n">
+        <v>194588335.1086689</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>4270722.341817826</v>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228120027_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>222550411.5857633</v>
+      </c>
+      <c r="B161" t="n">
+        <v>13748724.18937098</v>
+      </c>
+      <c r="C161" t="n">
+        <v>5952863.522230119</v>
+      </c>
+      <c r="D161" t="n">
+        <v>9275045.375978433</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>23023769.56534941</v>
+      </c>
+      <c r="G161" t="n">
+        <v>5952863.522230119</v>
+      </c>
+      <c r="H161" t="n">
+        <v>184401844.503344</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>9171933.994839802</v>
+      </c>
+      <c r="M161" t="n">
+        <v>222550411.5857633</v>
+      </c>
+      <c r="N161" t="n">
+        <v>61153.05595825515</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>61153.05595825515</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>61146.22663226733</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>6.829325979493733</v>
+      </c>
+      <c r="V161" t="n">
+        <v>1902.094000101089</v>
+      </c>
+      <c r="W161" t="n">
+        <v>220783973.3492245</v>
+      </c>
+      <c r="X161" t="n">
+        <v>222550411.5857633</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1766438.236538827</v>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228123536_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>194416410.4649049</v>
+      </c>
+      <c r="B162" t="n">
+        <v>13739798.96634003</v>
+      </c>
+      <c r="C162" t="n">
+        <v>5950072.29424317</v>
+      </c>
+      <c r="D162" t="n">
+        <v>9274602.627270846</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>23014401.59361088</v>
+      </c>
+      <c r="G162" t="n">
+        <v>5950072.29424317</v>
+      </c>
+      <c r="H162" t="n">
+        <v>156339552.0021738</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>9112384.574876999</v>
+      </c>
+      <c r="M162" t="n">
+        <v>194416410.4649049</v>
+      </c>
+      <c r="N162" t="n">
+        <v>60756.06478761139</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>60756.06478761139</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>60749.23049918015</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>6.834288431157773</v>
+      </c>
+      <c r="V162" t="n">
+        <v>1614.430999994278</v>
+      </c>
+      <c r="W162" t="n">
+        <v>190239051.4483885</v>
+      </c>
+      <c r="X162" t="n">
+        <v>194416410.4649049</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>4177359.016516358</v>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228131006_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>219964305.2621308</v>
+      </c>
+      <c r="B163" t="n">
+        <v>13745152.6155971</v>
+      </c>
+      <c r="C163" t="n">
+        <v>5951746.544758562</v>
+      </c>
+      <c r="D163" t="n">
+        <v>9090606.656386184</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="n">
+        <v>22835759.27198328</v>
+      </c>
+      <c r="G163" t="n">
+        <v>5951746.544758562</v>
+      </c>
+      <c r="H163" t="n">
+        <v>178242452.1764332</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>12934347.26895573</v>
+      </c>
+      <c r="M163" t="n">
+        <v>219964305.2621308</v>
+      </c>
+      <c r="N163" t="n">
+        <v>86235.49758457755</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>86235.49758457755</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>86228.98179303775</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>6.51579153998404</v>
+      </c>
+      <c r="V163" t="n">
+        <v>1149.105000019073</v>
+      </c>
+      <c r="W163" t="n">
+        <v>218481248.2429845</v>
+      </c>
+      <c r="X163" t="n">
+        <v>219964305.2621308</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1483057.019146353</v>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228134004_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>194590413.1639625</v>
+      </c>
+      <c r="B164" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C164" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D164" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G164" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H164" t="n">
+        <v>156504523.0974238</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M164" t="n">
+        <v>194590413.1639625</v>
+      </c>
+      <c r="N164" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V164" t="n">
+        <v>4.207000017166138</v>
+      </c>
+      <c r="W164" t="n">
+        <v>190353938.3149939</v>
+      </c>
+      <c r="X164" t="n">
+        <v>194590413.1639625</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>4236474.848968655</v>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228140202_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>224931071.7182764</v>
+      </c>
+      <c r="B165" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C165" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D165" t="n">
+        <v>9241260.748126749</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="n">
+        <v>22986413.17922617</v>
+      </c>
+      <c r="G165" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H165" t="n">
+        <v>186154235.4432818</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>9838676.551009862</v>
+      </c>
+      <c r="M165" t="n">
+        <v>224931071.7182764</v>
+      </c>
+      <c r="N165" t="n">
+        <v>65597.95077083209</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>65597.95077083209</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>65591.17700673267</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="n">
+        <v>6.773764099812912</v>
+      </c>
+      <c r="V165" t="n">
+        <v>3.353000164031982</v>
+      </c>
+      <c r="W165" t="n">
+        <v>220694596.8693077</v>
+      </c>
+      <c r="X165" t="n">
+        <v>224931071.7182764</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>4236474.848968714</v>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228140458_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>194433707.1141717</v>
+      </c>
+      <c r="B166" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C166" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D166" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G166" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H166" t="n">
+        <v>156347817.047633</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M166" t="n">
+        <v>194433707.1141717</v>
+      </c>
+      <c r="N166" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V166" t="n">
+        <v>4.232000112533569</v>
+      </c>
+      <c r="W166" t="n">
+        <v>190197232.2652034</v>
+      </c>
+      <c r="X166" t="n">
+        <v>194433707.1141717</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>4236474.848968357</v>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228140803_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>223173588.2693403</v>
+      </c>
+      <c r="B167" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C167" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D167" t="n">
+        <v>8939373.125831658</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="n">
+        <v>22684525.55693108</v>
+      </c>
+      <c r="G167" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H167" t="n">
+        <v>178495391.7549107</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>16041924.4127399</v>
+      </c>
+      <c r="M167" t="n">
+        <v>223173588.2693403</v>
+      </c>
+      <c r="N167" t="n">
+        <v>106952.4195783769</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>106952.4195783769</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>106946.162751599</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="n">
+        <v>6.256826778002083</v>
+      </c>
+      <c r="V167" t="n">
+        <v>3.501999855041504</v>
+      </c>
+      <c r="W167" t="n">
+        <v>218937113.4203718</v>
+      </c>
+      <c r="X167" t="n">
+        <v>223173588.2693403</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>4236474.848968536</v>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228141121_mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>83910597.11386395</v>
+      </c>
+      <c r="B168" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C168" t="n">
+        <v>5771618.800164824</v>
+      </c>
+      <c r="D168" t="n">
+        <v>36489985.37437859</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="n">
+        <v>48697133.66123348</v>
+      </c>
+      <c r="G168" t="n">
+        <v>5771618.800164824</v>
+      </c>
+      <c r="H168" t="n">
+        <v>7659642.947865215</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>21782201.70460043</v>
+      </c>
+      <c r="M168" t="n">
+        <v>83910597.11386395</v>
+      </c>
+      <c r="N168" t="n">
+        <v>145221.1893768969</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>145221.1893768969</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>145214.6780306701</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="n">
+        <v>6.511346228210095</v>
+      </c>
+      <c r="V168" t="n">
+        <v>1630.793999910355</v>
+      </c>
+      <c r="W168" t="n">
+        <v>82713836.31719294</v>
+      </c>
+      <c r="X168" t="n">
+        <v>83910597.11386395</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>1196760.796671003</v>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>oxy_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228141334_oxy_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>96208276.34909913</v>
+      </c>
+      <c r="B169" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C169" t="n">
+        <v>6742496.053220249</v>
+      </c>
+      <c r="D169" t="n">
+        <v>36489985.37437862</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="n">
+        <v>48697133.6612335</v>
+      </c>
+      <c r="G169" t="n">
+        <v>6742496.053220249</v>
+      </c>
+      <c r="H169" t="n">
+        <v>18986444.93004474</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>21782201.70460062</v>
+      </c>
+      <c r="M169" t="n">
+        <v>96208276.34909913</v>
+      </c>
+      <c r="N169" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>145214.6780306714</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>6.511346228210152</v>
+      </c>
+      <c r="V169" t="n">
+        <v>332.0119998455048</v>
+      </c>
+      <c r="W169" t="n">
+        <v>93979642.35672604</v>
+      </c>
+      <c r="X169" t="n">
+        <v>96208276.34909913</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>2228633.992373094</v>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>oxy_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228144414_oxy_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>83851860.5980399</v>
+      </c>
+      <c r="B170" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C170" t="n">
+        <v>5771618.800164822</v>
+      </c>
+      <c r="D170" t="n">
+        <v>36489985.37437854</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" t="n">
+        <v>48697133.66123343</v>
+      </c>
+      <c r="G170" t="n">
+        <v>5771618.800164822</v>
+      </c>
+      <c r="H170" t="n">
+        <v>7600906.43204147</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>21782201.70460018</v>
+      </c>
+      <c r="M170" t="n">
+        <v>83851860.5980399</v>
+      </c>
+      <c r="N170" t="n">
+        <v>145221.1893768952</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>145221.1893768952</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>145214.6780306684</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="n">
+        <v>6.511346228210019</v>
+      </c>
+      <c r="V170" t="n">
+        <v>1332.246999979019</v>
+      </c>
+      <c r="W170" t="n">
+        <v>82669615.53393583</v>
+      </c>
+      <c r="X170" t="n">
+        <v>83851860.5980399</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1182245.064104065</v>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>oxy_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228145201_oxy_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>95061189.54857171</v>
+      </c>
+      <c r="B171" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C171" t="n">
+        <v>5771618.800164826</v>
+      </c>
+      <c r="D171" t="n">
+        <v>36489985.37437855</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>48697133.66123344</v>
+      </c>
+      <c r="G171" t="n">
+        <v>5771618.800164826</v>
+      </c>
+      <c r="H171" t="n">
+        <v>18810235.3825732</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>21782201.70460024</v>
+      </c>
+      <c r="M171" t="n">
+        <v>95061189.54857171</v>
+      </c>
+      <c r="N171" t="n">
+        <v>145221.1893768955</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>145221.1893768955</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>145214.6780306709</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="n">
+        <v>6.511346228210129</v>
+      </c>
+      <c r="V171" t="n">
+        <v>349.9459998607635</v>
+      </c>
+      <c r="W171" t="n">
+        <v>92946332.93486884</v>
+      </c>
+      <c r="X171" t="n">
+        <v>95061189.54857171</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>2114856.613702863</v>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>oxy_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228151801_oxy_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>83900982.98507684</v>
+      </c>
+      <c r="B172" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C172" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D172" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G172" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H172" t="n">
+        <v>7660091.856915682</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M172" t="n">
+        <v>83900982.98507684</v>
+      </c>
+      <c r="N172" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V172" t="n">
+        <v>2.782000064849854</v>
+      </c>
+      <c r="W172" t="n">
+        <v>83900982.98511806</v>
+      </c>
+      <c r="X172" t="n">
+        <v>83900982.98507684</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>-4.121661186218262e-05</v>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228152604_oxy_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>95228682.78535719</v>
+      </c>
+      <c r="B173" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C173" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D173" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G173" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H173" t="n">
+        <v>18987791.65719603</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M173" t="n">
+        <v>95228682.78535719</v>
+      </c>
+      <c r="N173" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V173" t="n">
+        <v>2.531000137329102</v>
+      </c>
+      <c r="W173" t="n">
+        <v>95228682.78539808</v>
+      </c>
+      <c r="X173" t="n">
+        <v>95228682.78535719</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>-4.088878631591797e-05</v>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228152814_oxy_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>83842695.37830365</v>
+      </c>
+      <c r="B174" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C174" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D174" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G174" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H174" t="n">
+        <v>7601804.250142488</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M174" t="n">
+        <v>83842695.37830365</v>
+      </c>
+      <c r="N174" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V174" t="n">
+        <v>2.561000108718872</v>
+      </c>
+      <c r="W174" t="n">
+        <v>83842695.37834464</v>
+      </c>
+      <c r="X174" t="n">
+        <v>83842695.37830365</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>-4.09930944442749e-05</v>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228153217_oxy_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>95053819.96503763</v>
+      </c>
+      <c r="B175" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C175" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D175" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G175" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H175" t="n">
+        <v>18812928.83687647</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M175" t="n">
+        <v>95053819.96503763</v>
+      </c>
+      <c r="N175" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V175" t="n">
+        <v>2.634000062942505</v>
+      </c>
+      <c r="W175" t="n">
+        <v>95053819.96507847</v>
+      </c>
+      <c r="X175" t="n">
+        <v>95053819.96503763</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>-4.084408283233643e-05</v>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228153427_oxy_inflex_std_2_el_price_150</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE175"/>
+  <dimension ref="A1:AE191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18504,6 +18504,1654 @@
       <c r="AE175" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260228153427_oxy_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>194588335.1086689</v>
+      </c>
+      <c r="B176" t="n">
+        <v>13745152.54522158</v>
+      </c>
+      <c r="C176" t="n">
+        <v>5951746.544758614</v>
+      </c>
+      <c r="D176" t="n">
+        <v>9276606.51580389</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" t="n">
+        <v>23021759.06102547</v>
+      </c>
+      <c r="G176" t="n">
+        <v>5951746.544758614</v>
+      </c>
+      <c r="H176" t="n">
+        <v>156502444.9280091</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>9112384.574875714</v>
+      </c>
+      <c r="M176" t="n">
+        <v>194588335.1086689</v>
+      </c>
+      <c r="N176" t="n">
+        <v>60756.06478762638</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>60756.06478762638</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>60749.23049917693</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" t="n">
+        <v>6.834288431157401</v>
+      </c>
+      <c r="V176" t="n">
+        <v>1920.906000137329</v>
+      </c>
+      <c r="W176" t="n">
+        <v>190317612.7668511</v>
+      </c>
+      <c r="X176" t="n">
+        <v>194588335.1086689</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>4270722.341817826</v>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325132540_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>222550411.5857633</v>
+      </c>
+      <c r="B177" t="n">
+        <v>13748724.18937098</v>
+      </c>
+      <c r="C177" t="n">
+        <v>5952863.522230119</v>
+      </c>
+      <c r="D177" t="n">
+        <v>9275045.375978433</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="n">
+        <v>23023769.56534941</v>
+      </c>
+      <c r="G177" t="n">
+        <v>5952863.522230119</v>
+      </c>
+      <c r="H177" t="n">
+        <v>184401844.503344</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>9171933.994839802</v>
+      </c>
+      <c r="M177" t="n">
+        <v>222550411.5857633</v>
+      </c>
+      <c r="N177" t="n">
+        <v>61153.05595825515</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>61153.05595825515</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>61146.22663226733</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="n">
+        <v>6.829325979493733</v>
+      </c>
+      <c r="V177" t="n">
+        <v>2005.228000164032</v>
+      </c>
+      <c r="W177" t="n">
+        <v>220783973.3492245</v>
+      </c>
+      <c r="X177" t="n">
+        <v>222550411.5857633</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>1766438.236538827</v>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325140023_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>193758839.8699471</v>
+      </c>
+      <c r="B178" t="n">
+        <v>13739798.96691164</v>
+      </c>
+      <c r="C178" t="n">
+        <v>5950072.294242912</v>
+      </c>
+      <c r="D178" t="n">
+        <v>9274602.627270218</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" t="n">
+        <v>23014401.59418185</v>
+      </c>
+      <c r="G178" t="n">
+        <v>5950072.294242912</v>
+      </c>
+      <c r="H178" t="n">
+        <v>155681981.4066461</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>9112384.574876267</v>
+      </c>
+      <c r="M178" t="n">
+        <v>193758839.8699471</v>
+      </c>
+      <c r="N178" t="n">
+        <v>60756.06478760646</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>60756.06478760646</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>60749.23049917602</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>0</v>
+      </c>
+      <c r="U178" t="n">
+        <v>6.834288431157312</v>
+      </c>
+      <c r="V178" t="n">
+        <v>2178.197999954224</v>
+      </c>
+      <c r="W178" t="n">
+        <v>190237767.9942716</v>
+      </c>
+      <c r="X178" t="n">
+        <v>193758839.8699471</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>3521071.875675499</v>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325143620_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>225232042.2967354</v>
+      </c>
+      <c r="B179" t="n">
+        <v>13745152.4310994</v>
+      </c>
+      <c r="C179" t="n">
+        <v>5951746.544758588</v>
+      </c>
+      <c r="D179" t="n">
+        <v>8721504.131622389</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
+        <v>22466656.56272179</v>
+      </c>
+      <c r="G179" t="n">
+        <v>5951746.544758588</v>
+      </c>
+      <c r="H179" t="n">
+        <v>176294898.6613318</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>20518740.52792322</v>
+      </c>
+      <c r="M179" t="n">
+        <v>225232042.2967354</v>
+      </c>
+      <c r="N179" t="n">
+        <v>136797.4872782556</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>136797.4872782556</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>136791.6035194875</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="n">
+        <v>5.883758768403472</v>
+      </c>
+      <c r="V179" t="n">
+        <v>959.2840001583099</v>
+      </c>
+      <c r="W179" t="n">
+        <v>218475985.7634242</v>
+      </c>
+      <c r="X179" t="n">
+        <v>225232042.2967354</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>6756056.533311129</v>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325151522_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>194590413.1639625</v>
+      </c>
+      <c r="B180" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C180" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D180" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G180" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H180" t="n">
+        <v>156504523.0974238</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M180" t="n">
+        <v>194590413.1639625</v>
+      </c>
+      <c r="N180" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V180" t="n">
+        <v>3.534000158309937</v>
+      </c>
+      <c r="W180" t="n">
+        <v>190353938.3149939</v>
+      </c>
+      <c r="X180" t="n">
+        <v>194590413.1639625</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>4236474.848968655</v>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325153353_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>224931071.7182764</v>
+      </c>
+      <c r="B181" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C181" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D181" t="n">
+        <v>9241260.748126749</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" t="n">
+        <v>22986413.17922617</v>
+      </c>
+      <c r="G181" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H181" t="n">
+        <v>186154235.4432818</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>9838676.551009862</v>
+      </c>
+      <c r="M181" t="n">
+        <v>224931071.7182764</v>
+      </c>
+      <c r="N181" t="n">
+        <v>65597.95077083209</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>65597.95077083209</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>65591.17700673267</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="n">
+        <v>6.773764099812912</v>
+      </c>
+      <c r="V181" t="n">
+        <v>2.863000154495239</v>
+      </c>
+      <c r="W181" t="n">
+        <v>220694596.8693077</v>
+      </c>
+      <c r="X181" t="n">
+        <v>224931071.7182764</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>4236474.848968714</v>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325153629_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>194433707.1141717</v>
+      </c>
+      <c r="B182" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C182" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D182" t="n">
+        <v>9276606.515804293</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="n">
+        <v>23021758.94690371</v>
+      </c>
+      <c r="G182" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H182" t="n">
+        <v>156347817.047633</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M182" t="n">
+        <v>194433707.1141717</v>
+      </c>
+      <c r="N182" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V182" t="n">
+        <v>3.549000024795532</v>
+      </c>
+      <c r="W182" t="n">
+        <v>190197232.2652034</v>
+      </c>
+      <c r="X182" t="n">
+        <v>194433707.1141717</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>4236474.848968357</v>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325153911_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>223173588.2693403</v>
+      </c>
+      <c r="B183" t="n">
+        <v>13745152.43109942</v>
+      </c>
+      <c r="C183" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D183" t="n">
+        <v>8939373.125831658</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" t="n">
+        <v>22684525.55693108</v>
+      </c>
+      <c r="G183" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H183" t="n">
+        <v>178495391.7549107</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>16041924.4127399</v>
+      </c>
+      <c r="M183" t="n">
+        <v>223173588.2693403</v>
+      </c>
+      <c r="N183" t="n">
+        <v>106952.4195783769</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>106952.4195783769</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>106946.162751599</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="n">
+        <v>6.256826778002083</v>
+      </c>
+      <c r="V183" t="n">
+        <v>2.834000110626221</v>
+      </c>
+      <c r="W183" t="n">
+        <v>218937113.4203718</v>
+      </c>
+      <c r="X183" t="n">
+        <v>223173588.2693403</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>4236474.848968506</v>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325154203_mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>83910597.11386395</v>
+      </c>
+      <c r="B184" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C184" t="n">
+        <v>5771618.800164824</v>
+      </c>
+      <c r="D184" t="n">
+        <v>36489985.37437859</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="n">
+        <v>48697133.66123348</v>
+      </c>
+      <c r="G184" t="n">
+        <v>5771618.800164824</v>
+      </c>
+      <c r="H184" t="n">
+        <v>7659642.947865215</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>21782201.70460043</v>
+      </c>
+      <c r="M184" t="n">
+        <v>83910597.11386395</v>
+      </c>
+      <c r="N184" t="n">
+        <v>145221.1893768969</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>145221.1893768969</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>145214.6780306701</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
+      <c r="T184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="n">
+        <v>6.511346228210095</v>
+      </c>
+      <c r="V184" t="n">
+        <v>1438.56500005722</v>
+      </c>
+      <c r="W184" t="n">
+        <v>82713836.31719294</v>
+      </c>
+      <c r="X184" t="n">
+        <v>83910597.11386395</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>1196760.796671003</v>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>oxy_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325154409_oxy_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>96208276.34909913</v>
+      </c>
+      <c r="B185" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C185" t="n">
+        <v>6742496.053220249</v>
+      </c>
+      <c r="D185" t="n">
+        <v>36489985.37437862</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="n">
+        <v>48697133.6612335</v>
+      </c>
+      <c r="G185" t="n">
+        <v>6742496.053220249</v>
+      </c>
+      <c r="H185" t="n">
+        <v>18986444.93004474</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>21782201.70460062</v>
+      </c>
+      <c r="M185" t="n">
+        <v>96208276.34909913</v>
+      </c>
+      <c r="N185" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>145214.6780306714</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" t="n">
+        <v>6.511346228210152</v>
+      </c>
+      <c r="V185" t="n">
+        <v>281.3209998607635</v>
+      </c>
+      <c r="W185" t="n">
+        <v>93979642.35672604</v>
+      </c>
+      <c r="X185" t="n">
+        <v>96208276.34909913</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>2228633.992373094</v>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>oxy_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325161112_oxy_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>83851860.59804052</v>
+      </c>
+      <c r="B186" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C186" t="n">
+        <v>5771618.800164822</v>
+      </c>
+      <c r="D186" t="n">
+        <v>36489985.37437861</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>48697133.6612335</v>
+      </c>
+      <c r="G186" t="n">
+        <v>5771618.800164822</v>
+      </c>
+      <c r="H186" t="n">
+        <v>7600906.432041622</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>21782201.70460058</v>
+      </c>
+      <c r="M186" t="n">
+        <v>83851860.59804052</v>
+      </c>
+      <c r="N186" t="n">
+        <v>145221.1893768979</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>145221.1893768979</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V186" t="n">
+        <v>1432.384999990463</v>
+      </c>
+      <c r="W186" t="n">
+        <v>82669667.63602158</v>
+      </c>
+      <c r="X186" t="n">
+        <v>83851860.59804052</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>1182192.962018937</v>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>oxy_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325161800_oxy_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>95061189.5485726</v>
+      </c>
+      <c r="B187" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C187" t="n">
+        <v>5771618.800164828</v>
+      </c>
+      <c r="D187" t="n">
+        <v>36489985.37437861</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>48697133.6612335</v>
+      </c>
+      <c r="G187" t="n">
+        <v>5771618.800164828</v>
+      </c>
+      <c r="H187" t="n">
+        <v>18810235.38257373</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>21782201.70460055</v>
+      </c>
+      <c r="M187" t="n">
+        <v>95061189.5485726</v>
+      </c>
+      <c r="N187" t="n">
+        <v>145221.1893768976</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>145221.1893768976</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>145214.6780306709</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="n">
+        <v>6.51134622821013</v>
+      </c>
+      <c r="V187" t="n">
+        <v>329.106999874115</v>
+      </c>
+      <c r="W187" t="n">
+        <v>92948211.40862112</v>
+      </c>
+      <c r="X187" t="n">
+        <v>95061189.5485726</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>2112978.139951482</v>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>oxy_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325164507_oxy_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>83900982.98507684</v>
+      </c>
+      <c r="B188" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C188" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D188" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G188" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H188" t="n">
+        <v>7660091.856915682</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M188" t="n">
+        <v>83900982.98507684</v>
+      </c>
+      <c r="N188" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U188" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V188" t="n">
+        <v>2.38700008392334</v>
+      </c>
+      <c r="W188" t="n">
+        <v>83900982.98511806</v>
+      </c>
+      <c r="X188" t="n">
+        <v>83900982.98507684</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>-4.121661186218262e-05</v>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325165241_oxy_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>95228682.78535719</v>
+      </c>
+      <c r="B189" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C189" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D189" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G189" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H189" t="n">
+        <v>18987791.65719603</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M189" t="n">
+        <v>95228682.78535719</v>
+      </c>
+      <c r="N189" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V189" t="n">
+        <v>2.272000074386597</v>
+      </c>
+      <c r="W189" t="n">
+        <v>95228682.78539808</v>
+      </c>
+      <c r="X189" t="n">
+        <v>95228682.78535719</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>-4.088878631591797e-05</v>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325165444_oxy_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>83842695.37830365</v>
+      </c>
+      <c r="B190" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C190" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D190" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G190" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H190" t="n">
+        <v>7601804.250142488</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M190" t="n">
+        <v>83842695.37830365</v>
+      </c>
+      <c r="N190" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V190" t="n">
+        <v>2.324000120162964</v>
+      </c>
+      <c r="W190" t="n">
+        <v>83842695.37834466</v>
+      </c>
+      <c r="X190" t="n">
+        <v>83842695.37830365</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>-4.100799560546875e-05</v>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325165814_oxy_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>95053819.96503763</v>
+      </c>
+      <c r="B191" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C191" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D191" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G191" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H191" t="n">
+        <v>18812928.83687647</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M191" t="n">
+        <v>95053819.96503763</v>
+      </c>
+      <c r="N191" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V191" t="n">
+        <v>2.470999956130981</v>
+      </c>
+      <c r="W191" t="n">
+        <v>95053819.96507847</v>
+      </c>
+      <c r="X191" t="n">
+        <v>95053819.96503763</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>-4.084408283233643e-05</v>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325170017_oxy_inflex_std_2_el_price_150</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE191"/>
+  <dimension ref="A1:AE207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20152,6 +20152,1654 @@
       <c r="AE191" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325170017_oxy_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>195232967.6952649</v>
+      </c>
+      <c r="B192" t="n">
+        <v>14288980.0594945</v>
+      </c>
+      <c r="C192" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="D192" t="n">
+        <v>9375333.418723084</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>23664313.47821758</v>
+      </c>
+      <c r="G192" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="H192" t="n">
+        <v>156504523.0974131</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M192" t="n">
+        <v>195232967.6952649</v>
+      </c>
+      <c r="N192" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>60749.23049917667</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="n">
+        <v>6.834288431157372</v>
+      </c>
+      <c r="V192" t="n">
+        <v>3241.892999887466</v>
+      </c>
+      <c r="W192" t="n">
+        <v>190820186.9626811</v>
+      </c>
+      <c r="X192" t="n">
+        <v>195232967.6952649</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>4412780.73258388</v>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325183935_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>224266256.930155</v>
+      </c>
+      <c r="B193" t="n">
+        <v>14283389.83912783</v>
+      </c>
+      <c r="C193" t="n">
+        <v>5950072.294242965</v>
+      </c>
+      <c r="D193" t="n">
+        <v>9356490.139279384</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>23639879.97840722</v>
+      </c>
+      <c r="G193" t="n">
+        <v>5950072.294242965</v>
+      </c>
+      <c r="H193" t="n">
+        <v>185218784.0538888</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>9457520.603616001</v>
+      </c>
+      <c r="M193" t="n">
+        <v>224266256.930155</v>
+      </c>
+      <c r="N193" t="n">
+        <v>63056.94288453033</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>63056.94288453033</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>63050.13735743917</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="n">
+        <v>6.805527095429129</v>
+      </c>
+      <c r="V193" t="n">
+        <v>4036.899999856949</v>
+      </c>
+      <c r="W193" t="n">
+        <v>221307374.4127661</v>
+      </c>
+      <c r="X193" t="n">
+        <v>224266256.930155</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>2958882.51738891</v>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325193619_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>195076261.645474</v>
+      </c>
+      <c r="B194" t="n">
+        <v>14288980.0594945</v>
+      </c>
+      <c r="C194" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="D194" t="n">
+        <v>9375333.418723086</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>23664313.47821759</v>
+      </c>
+      <c r="G194" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="H194" t="n">
+        <v>156347817.0476221</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M194" t="n">
+        <v>195076261.645474</v>
+      </c>
+      <c r="N194" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>60749.23049917666</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V194" t="n">
+        <v>1025.335999965668</v>
+      </c>
+      <c r="W194" t="n">
+        <v>190746358.7571647</v>
+      </c>
+      <c r="X194" t="n">
+        <v>195076261.645474</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>4329902.88830936</v>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325204609_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>221601617.4642582</v>
+      </c>
+      <c r="B195" t="n">
+        <v>14283389.84376562</v>
+      </c>
+      <c r="C195" t="n">
+        <v>5950072.29424291</v>
+      </c>
+      <c r="D195" t="n">
+        <v>9090643.510335527</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>23374033.35410115</v>
+      </c>
+      <c r="G195" t="n">
+        <v>5950072.29424291</v>
+      </c>
+      <c r="H195" t="n">
+        <v>177357320.9643199</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>14920190.85159429</v>
+      </c>
+      <c r="M195" t="n">
+        <v>221601617.4642582</v>
+      </c>
+      <c r="N195" t="n">
+        <v>99474.28931519316</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>99474.28931519316</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>99467.93901062316</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="n">
+        <v>0</v>
+      </c>
+      <c r="T195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="n">
+        <v>6.350304574764222</v>
+      </c>
+      <c r="V195" t="n">
+        <v>1193.398000001907</v>
+      </c>
+      <c r="W195" t="n">
+        <v>219074333.5689138</v>
+      </c>
+      <c r="X195" t="n">
+        <v>221601617.4642582</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>2527283.895344466</v>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325210558_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195232967.6952768</v>
+      </c>
+      <c r="B196" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C196" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D196" t="n">
+        <v>9375333.418723509</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>23664313.47821799</v>
+      </c>
+      <c r="G196" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H196" t="n">
+        <v>156504523.0974238</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M196" t="n">
+        <v>195232967.6952768</v>
+      </c>
+      <c r="N196" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V196" t="n">
+        <v>3.54200005531311</v>
+      </c>
+      <c r="W196" t="n">
+        <v>190996492.8463081</v>
+      </c>
+      <c r="X196" t="n">
+        <v>195232967.6952768</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>4236474.848968625</v>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325212824_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>225573626.2495907</v>
+      </c>
+      <c r="B197" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C197" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D197" t="n">
+        <v>9339987.651045963</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="n">
+        <v>23628967.71054045</v>
+      </c>
+      <c r="G197" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H197" t="n">
+        <v>186154235.4432818</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>9838676.551009862</v>
+      </c>
+      <c r="M197" t="n">
+        <v>225573626.2495907</v>
+      </c>
+      <c r="N197" t="n">
+        <v>65597.95077083209</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>65597.95077083209</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>65591.17700673267</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" t="n">
+        <v>6.773764099812912</v>
+      </c>
+      <c r="V197" t="n">
+        <v>2.819000005722046</v>
+      </c>
+      <c r="W197" t="n">
+        <v>221337151.400622</v>
+      </c>
+      <c r="X197" t="n">
+        <v>225573626.2495907</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>4236474.848968714</v>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325213101_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>195076261.645486</v>
+      </c>
+      <c r="B198" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C198" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D198" t="n">
+        <v>9375333.418723509</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" t="n">
+        <v>23664313.47821799</v>
+      </c>
+      <c r="G198" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H198" t="n">
+        <v>156347817.047633</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M198" t="n">
+        <v>195076261.645486</v>
+      </c>
+      <c r="N198" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="n">
+        <v>0</v>
+      </c>
+      <c r="T198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V198" t="n">
+        <v>3.571000099182129</v>
+      </c>
+      <c r="W198" t="n">
+        <v>190839786.7965176</v>
+      </c>
+      <c r="X198" t="n">
+        <v>195076261.645486</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>4236474.848968327</v>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325213343_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>223816142.8006546</v>
+      </c>
+      <c r="B199" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C199" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D199" t="n">
+        <v>9038100.028750874</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>23327080.08824536</v>
+      </c>
+      <c r="G199" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H199" t="n">
+        <v>178495391.7549107</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>16041924.4127399</v>
+      </c>
+      <c r="M199" t="n">
+        <v>223816142.8006546</v>
+      </c>
+      <c r="N199" t="n">
+        <v>106952.4195783769</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>106952.4195783769</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>106946.162751599</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
+      <c r="T199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="n">
+        <v>6.256826778002083</v>
+      </c>
+      <c r="V199" t="n">
+        <v>2.991999864578247</v>
+      </c>
+      <c r="W199" t="n">
+        <v>219579667.9516861</v>
+      </c>
+      <c r="X199" t="n">
+        <v>223816142.8006546</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>4236474.848968536</v>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325213634_mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>84881474.36691967</v>
+      </c>
+      <c r="B200" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C200" t="n">
+        <v>6742496.053220249</v>
+      </c>
+      <c r="D200" t="n">
+        <v>36489985.37437862</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>48697133.6612335</v>
+      </c>
+      <c r="G200" t="n">
+        <v>6742496.053220249</v>
+      </c>
+      <c r="H200" t="n">
+        <v>7659642.947865287</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>21782201.70460062</v>
+      </c>
+      <c r="M200" t="n">
+        <v>84881474.36691967</v>
+      </c>
+      <c r="N200" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>145214.6780306714</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="n">
+        <v>0</v>
+      </c>
+      <c r="T200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="n">
+        <v>6.511346228210152</v>
+      </c>
+      <c r="V200" t="n">
+        <v>942.3729999065399</v>
+      </c>
+      <c r="W200" t="n">
+        <v>83149293.14447895</v>
+      </c>
+      <c r="X200" t="n">
+        <v>84881474.36691967</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1732181.22244072</v>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>oxy_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325213839_oxy_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>96208276.34909913</v>
+      </c>
+      <c r="B201" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C201" t="n">
+        <v>6742496.053220249</v>
+      </c>
+      <c r="D201" t="n">
+        <v>36489985.37437862</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="n">
+        <v>48697133.6612335</v>
+      </c>
+      <c r="G201" t="n">
+        <v>6742496.053220249</v>
+      </c>
+      <c r="H201" t="n">
+        <v>18986444.93004474</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>21782201.70460062</v>
+      </c>
+      <c r="M201" t="n">
+        <v>96208276.34909913</v>
+      </c>
+      <c r="N201" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>145214.6780306714</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
+      <c r="T201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="n">
+        <v>6.511346228210152</v>
+      </c>
+      <c r="V201" t="n">
+        <v>312.0910000801086</v>
+      </c>
+      <c r="W201" t="n">
+        <v>93994748.48821224</v>
+      </c>
+      <c r="X201" t="n">
+        <v>96208276.34909913</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>2213527.860886887</v>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>oxy_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325215724_oxy_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>84822737.851096</v>
+      </c>
+      <c r="B202" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C202" t="n">
+        <v>6742496.053220249</v>
+      </c>
+      <c r="D202" t="n">
+        <v>36489985.37437862</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="n">
+        <v>48697133.6612335</v>
+      </c>
+      <c r="G202" t="n">
+        <v>6742496.053220249</v>
+      </c>
+      <c r="H202" t="n">
+        <v>7600906.432041639</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>21782201.70460062</v>
+      </c>
+      <c r="M202" t="n">
+        <v>84822737.851096</v>
+      </c>
+      <c r="N202" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>145214.6780306714</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" t="n">
+        <v>0</v>
+      </c>
+      <c r="U202" t="n">
+        <v>6.511346228210152</v>
+      </c>
+      <c r="V202" t="n">
+        <v>1357.818999767303</v>
+      </c>
+      <c r="W202" t="n">
+        <v>82669282.24580833</v>
+      </c>
+      <c r="X202" t="n">
+        <v>84822737.851096</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>2153455.605287671</v>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>oxy_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325220443_oxy_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>95061189.54857276</v>
+      </c>
+      <c r="B203" t="n">
+        <v>12207148.28685488</v>
+      </c>
+      <c r="C203" t="n">
+        <v>5771618.800164824</v>
+      </c>
+      <c r="D203" t="n">
+        <v>36489985.37437863</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="n">
+        <v>48697133.66123351</v>
+      </c>
+      <c r="G203" t="n">
+        <v>5771618.800164824</v>
+      </c>
+      <c r="H203" t="n">
+        <v>18810235.38257379</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>21782201.70460063</v>
+      </c>
+      <c r="M203" t="n">
+        <v>95061189.54857276</v>
+      </c>
+      <c r="N203" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>145221.1893768982</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>145214.6780306714</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="n">
+        <v>6.511346228210154</v>
+      </c>
+      <c r="V203" t="n">
+        <v>378.6210000514984</v>
+      </c>
+      <c r="W203" t="n">
+        <v>92948701.75390178</v>
+      </c>
+      <c r="X203" t="n">
+        <v>95061189.54857276</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>2112487.794670984</v>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>oxy_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325223034_oxy_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>83900982.98507684</v>
+      </c>
+      <c r="B204" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C204" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D204" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G204" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H204" t="n">
+        <v>7660091.856915682</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M204" t="n">
+        <v>83900982.98507684</v>
+      </c>
+      <c r="N204" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="n">
+        <v>0</v>
+      </c>
+      <c r="T204" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2.463000059127808</v>
+      </c>
+      <c r="W204" t="n">
+        <v>83900982.98511806</v>
+      </c>
+      <c r="X204" t="n">
+        <v>83900982.98507684</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>-4.121661186218262e-05</v>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325223900_oxy_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>95228682.78535719</v>
+      </c>
+      <c r="B205" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C205" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D205" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G205" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H205" t="n">
+        <v>18987791.65719603</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M205" t="n">
+        <v>95228682.78535719</v>
+      </c>
+      <c r="N205" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="n">
+        <v>0</v>
+      </c>
+      <c r="T205" t="n">
+        <v>0</v>
+      </c>
+      <c r="U205" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V205" t="n">
+        <v>2.218000173568726</v>
+      </c>
+      <c r="W205" t="n">
+        <v>95228682.78539808</v>
+      </c>
+      <c r="X205" t="n">
+        <v>95228682.78535719</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>-4.088878631591797e-05</v>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325224112_oxy_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>83842695.37830365</v>
+      </c>
+      <c r="B206" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C206" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D206" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G206" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H206" t="n">
+        <v>7601804.250142488</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M206" t="n">
+        <v>83842695.37830365</v>
+      </c>
+      <c r="N206" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="n">
+        <v>0</v>
+      </c>
+      <c r="T206" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V206" t="n">
+        <v>2.284999847412109</v>
+      </c>
+      <c r="W206" t="n">
+        <v>83842695.37834464</v>
+      </c>
+      <c r="X206" t="n">
+        <v>83842695.37830365</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>-4.09930944442749e-05</v>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325224439_oxy_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>95053819.96503763</v>
+      </c>
+      <c r="B207" t="n">
+        <v>12204845.78141507</v>
+      </c>
+      <c r="C207" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="D207" t="n">
+        <v>36483821.36884278</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
+        <v>48688667.15025785</v>
+      </c>
+      <c r="G207" t="n">
+        <v>5770022.273296411</v>
+      </c>
+      <c r="H207" t="n">
+        <v>18812928.83687647</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>21782201.70460691</v>
+      </c>
+      <c r="M207" t="n">
+        <v>95053819.96503763</v>
+      </c>
+      <c r="N207" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>145221.189376899</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>145214.6780306711</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="n">
+        <v>6.511346228210139</v>
+      </c>
+      <c r="V207" t="n">
+        <v>2.266999959945679</v>
+      </c>
+      <c r="W207" t="n">
+        <v>95053819.96507847</v>
+      </c>
+      <c r="X207" t="n">
+        <v>95053819.96503763</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>-4.084408283233643e-05</v>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>oxy_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325224645_oxy_inflex_std_2_el_price_150</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE207"/>
+  <dimension ref="A1:AE231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21800,6 +21800,2478 @@
       <c r="AE207" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260325224645_oxy_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>195232967.6952649</v>
+      </c>
+      <c r="B208" t="n">
+        <v>14288980.0594945</v>
+      </c>
+      <c r="C208" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="D208" t="n">
+        <v>9375333.418723084</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>23664313.47821758</v>
+      </c>
+      <c r="G208" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="H208" t="n">
+        <v>156504523.0974131</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M208" t="n">
+        <v>195232967.6952649</v>
+      </c>
+      <c r="N208" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>60749.23049917667</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="n">
+        <v>6.834288431157372</v>
+      </c>
+      <c r="V208" t="n">
+        <v>2932.40099978447</v>
+      </c>
+      <c r="W208" t="n">
+        <v>190820186.9626811</v>
+      </c>
+      <c r="X208" t="n">
+        <v>195232967.6952649</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>4412780.73258388</v>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330181527_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>211711741.3530917</v>
+      </c>
+      <c r="B209" t="n">
+        <v>14294575.37990644</v>
+      </c>
+      <c r="C209" t="n">
+        <v>5953422.254316125</v>
+      </c>
+      <c r="D209" t="n">
+        <v>9377382.071823858</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>23671957.4517303</v>
+      </c>
+      <c r="G209" t="n">
+        <v>5953422.254316125</v>
+      </c>
+      <c r="H209" t="n">
+        <v>172973977.0721688</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>9112384.57487651</v>
+      </c>
+      <c r="M209" t="n">
+        <v>211711741.3530917</v>
+      </c>
+      <c r="N209" t="n">
+        <v>60756.06478760875</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>60756.06478760875</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>60749.23049917701</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>6.834288431157425</v>
+      </c>
+      <c r="V209" t="n">
+        <v>3913.080000162125</v>
+      </c>
+      <c r="W209" t="n">
+        <v>208267631.5231476</v>
+      </c>
+      <c r="X209" t="n">
+        <v>211711741.3530917</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>3444109.829944164</v>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330190702_mea_std_1_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>224266256.930155</v>
+      </c>
+      <c r="B210" t="n">
+        <v>14283389.83912783</v>
+      </c>
+      <c r="C210" t="n">
+        <v>5950072.294242965</v>
+      </c>
+      <c r="D210" t="n">
+        <v>9356490.139279384</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
+        <v>23639879.97840722</v>
+      </c>
+      <c r="G210" t="n">
+        <v>5950072.294242965</v>
+      </c>
+      <c r="H210" t="n">
+        <v>185218784.0538888</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>9457520.603616001</v>
+      </c>
+      <c r="M210" t="n">
+        <v>224266256.930155</v>
+      </c>
+      <c r="N210" t="n">
+        <v>63056.94288453033</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>63056.94288453033</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>63050.13735743917</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>6.805527095429129</v>
+      </c>
+      <c r="V210" t="n">
+        <v>3677.275000095367</v>
+      </c>
+      <c r="W210" t="n">
+        <v>221307374.4127661</v>
+      </c>
+      <c r="X210" t="n">
+        <v>224266256.930155</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>2958882.51738891</v>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330201446_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>195076261.645474</v>
+      </c>
+      <c r="B211" t="n">
+        <v>14288980.0594945</v>
+      </c>
+      <c r="C211" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="D211" t="n">
+        <v>9375333.418723086</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="n">
+        <v>23664313.47821759</v>
+      </c>
+      <c r="G211" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="H211" t="n">
+        <v>156347817.0476221</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M211" t="n">
+        <v>195076261.645474</v>
+      </c>
+      <c r="N211" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>60749.23049917666</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V211" t="n">
+        <v>976.6489999294281</v>
+      </c>
+      <c r="W211" t="n">
+        <v>190746358.7571647</v>
+      </c>
+      <c r="X211" t="n">
+        <v>195076261.645474</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>4329902.88830936</v>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330211846_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>208945030.3499798</v>
+      </c>
+      <c r="B212" t="n">
+        <v>14283389.86062343</v>
+      </c>
+      <c r="C212" t="n">
+        <v>5950072.294242965</v>
+      </c>
+      <c r="D212" t="n">
+        <v>9359386.07205661</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>23642775.93268004</v>
+      </c>
+      <c r="G212" t="n">
+        <v>5950072.294242965</v>
+      </c>
+      <c r="H212" t="n">
+        <v>169954167.7312917</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>9398014.391765134</v>
+      </c>
+      <c r="M212" t="n">
+        <v>208945030.3499798</v>
+      </c>
+      <c r="N212" t="n">
+        <v>62660.23976437888</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>62660.23976437888</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>62653.42927843358</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>6.810485946416623</v>
+      </c>
+      <c r="V212" t="n">
+        <v>1477.289000034332</v>
+      </c>
+      <c r="W212" t="n">
+        <v>207533394.9287854</v>
+      </c>
+      <c r="X212" t="n">
+        <v>208945030.3499798</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1411635.421194464</v>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330213736_mea_std_2_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>221601617.4642582</v>
+      </c>
+      <c r="B213" t="n">
+        <v>14283389.84376562</v>
+      </c>
+      <c r="C213" t="n">
+        <v>5950072.29424291</v>
+      </c>
+      <c r="D213" t="n">
+        <v>9090643.510335527</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="n">
+        <v>23374033.35410115</v>
+      </c>
+      <c r="G213" t="n">
+        <v>5950072.29424291</v>
+      </c>
+      <c r="H213" t="n">
+        <v>177357320.9643199</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>14920190.85159429</v>
+      </c>
+      <c r="M213" t="n">
+        <v>221601617.4642582</v>
+      </c>
+      <c r="N213" t="n">
+        <v>99474.28931519316</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>99474.28931519316</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>99467.93901062316</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>6.350304574764222</v>
+      </c>
+      <c r="V213" t="n">
+        <v>1043.353000164032</v>
+      </c>
+      <c r="W213" t="n">
+        <v>219074333.5689138</v>
+      </c>
+      <c r="X213" t="n">
+        <v>221601617.4642582</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>2527283.895344466</v>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330220451_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>195232967.6952768</v>
+      </c>
+      <c r="B214" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C214" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D214" t="n">
+        <v>9375333.418723509</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="n">
+        <v>23664313.47821799</v>
+      </c>
+      <c r="G214" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H214" t="n">
+        <v>156504523.0974238</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M214" t="n">
+        <v>195232967.6952768</v>
+      </c>
+      <c r="N214" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V214" t="n">
+        <v>3.604000091552734</v>
+      </c>
+      <c r="W214" t="n">
+        <v>190996492.8463081</v>
+      </c>
+      <c r="X214" t="n">
+        <v>195232967.6952768</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>4236474.848968625</v>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330222457_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>212587113.7204228</v>
+      </c>
+      <c r="B215" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C215" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D215" t="n">
+        <v>9370697.908208419</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="n">
+        <v>23659677.9677029</v>
+      </c>
+      <c r="G215" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H215" t="n">
+        <v>173768053.2263788</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>9207635.981582437</v>
+      </c>
+      <c r="M215" t="n">
+        <v>212587113.7204228</v>
+      </c>
+      <c r="N215" t="n">
+        <v>61391.06622803005</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>61391.06622803005</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>61384.23987721652</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0</v>
+      </c>
+      <c r="T215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="n">
+        <v>6.826350813931863</v>
+      </c>
+      <c r="V215" t="n">
+        <v>3.135999917984009</v>
+      </c>
+      <c r="W215" t="n">
+        <v>208350638.8714543</v>
+      </c>
+      <c r="X215" t="n">
+        <v>212587113.7204228</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>4236474.848968506</v>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330222749_mea_inflex_std_1_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>225573626.2495907</v>
+      </c>
+      <c r="B216" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C216" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D216" t="n">
+        <v>9339987.651045963</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="n">
+        <v>23628967.71054045</v>
+      </c>
+      <c r="G216" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H216" t="n">
+        <v>186154235.4432818</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>9838676.551009862</v>
+      </c>
+      <c r="M216" t="n">
+        <v>225573626.2495907</v>
+      </c>
+      <c r="N216" t="n">
+        <v>65597.95077083209</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>65597.95077083209</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>65591.17700673267</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="n">
+        <v>6.773764099812912</v>
+      </c>
+      <c r="V216" t="n">
+        <v>2.975000143051147</v>
+      </c>
+      <c r="W216" t="n">
+        <v>221337151.400622</v>
+      </c>
+      <c r="X216" t="n">
+        <v>225573626.2495907</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>4236474.848968714</v>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330222955_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>195076261.645486</v>
+      </c>
+      <c r="B217" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C217" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D217" t="n">
+        <v>9375333.418723509</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="n">
+        <v>23664313.47821799</v>
+      </c>
+      <c r="G217" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H217" t="n">
+        <v>156347817.047633</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M217" t="n">
+        <v>195076261.645486</v>
+      </c>
+      <c r="N217" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="n">
+        <v>0</v>
+      </c>
+      <c r="T217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V217" t="n">
+        <v>3.811000108718872</v>
+      </c>
+      <c r="W217" t="n">
+        <v>190839786.7965176</v>
+      </c>
+      <c r="X217" t="n">
+        <v>195076261.645486</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>4236474.848968327</v>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330223256_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>212091020.4761293</v>
+      </c>
+      <c r="B218" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C218" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D218" t="n">
+        <v>9339408.212231576</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="n">
+        <v>23628388.27172606</v>
+      </c>
+      <c r="G218" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H218" t="n">
+        <v>172660302.6827965</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>9850582.976848116</v>
+      </c>
+      <c r="M218" t="n">
+        <v>212091020.4761293</v>
+      </c>
+      <c r="N218" t="n">
+        <v>65677.32595088494</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>65677.32595088494</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>65670.55317898768</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" t="n">
+        <v>0</v>
+      </c>
+      <c r="T218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="n">
+        <v>6.772771897659724</v>
+      </c>
+      <c r="V218" t="n">
+        <v>3.128000020980835</v>
+      </c>
+      <c r="W218" t="n">
+        <v>207854545.6271607</v>
+      </c>
+      <c r="X218" t="n">
+        <v>212091020.4761293</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>4236474.848968655</v>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330223502_mea_inflex_std_2_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>223816142.8006546</v>
+      </c>
+      <c r="B219" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C219" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D219" t="n">
+        <v>9038100.028750874</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>23327080.08824536</v>
+      </c>
+      <c r="G219" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H219" t="n">
+        <v>178495391.7549107</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>16041924.4127399</v>
+      </c>
+      <c r="M219" t="n">
+        <v>223816142.8006546</v>
+      </c>
+      <c r="N219" t="n">
+        <v>106952.4195783769</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>106952.4195783769</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>106946.162751599</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="n">
+        <v>0</v>
+      </c>
+      <c r="T219" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" t="n">
+        <v>6.256826778002083</v>
+      </c>
+      <c r="V219" t="n">
+        <v>3.119999885559082</v>
+      </c>
+      <c r="W219" t="n">
+        <v>219579667.9516861</v>
+      </c>
+      <c r="X219" t="n">
+        <v>223816142.8006546</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>4236474.848968536</v>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260330223818_mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>195232967.6952649</v>
+      </c>
+      <c r="B220" t="n">
+        <v>14288980.0594945</v>
+      </c>
+      <c r="C220" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="D220" t="n">
+        <v>9375333.418723084</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
+        <v>23664313.47821758</v>
+      </c>
+      <c r="G220" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="H220" t="n">
+        <v>156504523.0974131</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M220" t="n">
+        <v>195232967.6952649</v>
+      </c>
+      <c r="N220" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>60749.23049917667</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="n">
+        <v>6.834288431157372</v>
+      </c>
+      <c r="V220" t="n">
+        <v>3150.179000139236</v>
+      </c>
+      <c r="W220" t="n">
+        <v>190820186.9626811</v>
+      </c>
+      <c r="X220" t="n">
+        <v>195232967.6952649</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>4412780.73258388</v>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331115914_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>211711741.3530917</v>
+      </c>
+      <c r="B221" t="n">
+        <v>14294575.37990644</v>
+      </c>
+      <c r="C221" t="n">
+        <v>5953422.254316125</v>
+      </c>
+      <c r="D221" t="n">
+        <v>9377382.071823858</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="n">
+        <v>23671957.4517303</v>
+      </c>
+      <c r="G221" t="n">
+        <v>5953422.254316125</v>
+      </c>
+      <c r="H221" t="n">
+        <v>172973977.0721688</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>9112384.57487651</v>
+      </c>
+      <c r="M221" t="n">
+        <v>211711741.3530917</v>
+      </c>
+      <c r="N221" t="n">
+        <v>60756.06478760875</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>60756.06478760875</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>60749.23049917701</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>6.834288431157425</v>
+      </c>
+      <c r="V221" t="n">
+        <v>4012.940999984741</v>
+      </c>
+      <c r="W221" t="n">
+        <v>208267631.5231476</v>
+      </c>
+      <c r="X221" t="n">
+        <v>211711741.3530917</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>3444109.829944164</v>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331125435_mea_std_1_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>224266256.930155</v>
+      </c>
+      <c r="B222" t="n">
+        <v>14283389.83912783</v>
+      </c>
+      <c r="C222" t="n">
+        <v>5950072.294242965</v>
+      </c>
+      <c r="D222" t="n">
+        <v>9356490.139279384</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" t="n">
+        <v>23639879.97840722</v>
+      </c>
+      <c r="G222" t="n">
+        <v>5950072.294242965</v>
+      </c>
+      <c r="H222" t="n">
+        <v>185218784.0538888</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>9457520.603616001</v>
+      </c>
+      <c r="M222" t="n">
+        <v>224266256.930155</v>
+      </c>
+      <c r="N222" t="n">
+        <v>63056.94288453033</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>63056.94288453033</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>63050.13735743917</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>6.805527095429129</v>
+      </c>
+      <c r="V222" t="n">
+        <v>3683.368000030518</v>
+      </c>
+      <c r="W222" t="n">
+        <v>221307374.4127661</v>
+      </c>
+      <c r="X222" t="n">
+        <v>224266256.930155</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>2958882.51738891</v>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331140413_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>195076261.645474</v>
+      </c>
+      <c r="B223" t="n">
+        <v>14288980.0594945</v>
+      </c>
+      <c r="C223" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="D223" t="n">
+        <v>9375333.418723086</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="n">
+        <v>23664313.47821759</v>
+      </c>
+      <c r="G223" t="n">
+        <v>5951746.544758597</v>
+      </c>
+      <c r="H223" t="n">
+        <v>156347817.0476221</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M223" t="n">
+        <v>195076261.645474</v>
+      </c>
+      <c r="N223" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>60749.23049917666</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="n">
+        <v>0</v>
+      </c>
+      <c r="T223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V223" t="n">
+        <v>982.8420000076294</v>
+      </c>
+      <c r="W223" t="n">
+        <v>190746358.7571647</v>
+      </c>
+      <c r="X223" t="n">
+        <v>195076261.645474</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>4329902.88830936</v>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331150818_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>208945030.3499798</v>
+      </c>
+      <c r="B224" t="n">
+        <v>14283389.86062343</v>
+      </c>
+      <c r="C224" t="n">
+        <v>5950072.294242965</v>
+      </c>
+      <c r="D224" t="n">
+        <v>9359386.07205661</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="n">
+        <v>23642775.93268004</v>
+      </c>
+      <c r="G224" t="n">
+        <v>5950072.294242965</v>
+      </c>
+      <c r="H224" t="n">
+        <v>169954167.7312917</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>9398014.391765134</v>
+      </c>
+      <c r="M224" t="n">
+        <v>208945030.3499798</v>
+      </c>
+      <c r="N224" t="n">
+        <v>62660.23976437888</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>62660.23976437888</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>62653.42927843358</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="n">
+        <v>6.810485946416623</v>
+      </c>
+      <c r="V224" t="n">
+        <v>1495.202000141144</v>
+      </c>
+      <c r="W224" t="n">
+        <v>207533394.9287854</v>
+      </c>
+      <c r="X224" t="n">
+        <v>208945030.3499798</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>1411635.421194464</v>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331152711_mea_std_2_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>221601617.4642582</v>
+      </c>
+      <c r="B225" t="n">
+        <v>14283389.84376562</v>
+      </c>
+      <c r="C225" t="n">
+        <v>5950072.29424291</v>
+      </c>
+      <c r="D225" t="n">
+        <v>9090643.510335527</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="n">
+        <v>23374033.35410115</v>
+      </c>
+      <c r="G225" t="n">
+        <v>5950072.29424291</v>
+      </c>
+      <c r="H225" t="n">
+        <v>177357320.9643199</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>14920190.85159429</v>
+      </c>
+      <c r="M225" t="n">
+        <v>221601617.4642582</v>
+      </c>
+      <c r="N225" t="n">
+        <v>99474.28931519316</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>99474.28931519316</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>99467.93901062316</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
+      <c r="T225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="n">
+        <v>6.350304574764222</v>
+      </c>
+      <c r="V225" t="n">
+        <v>1039.778000116348</v>
+      </c>
+      <c r="W225" t="n">
+        <v>219074333.5689138</v>
+      </c>
+      <c r="X225" t="n">
+        <v>221601617.4642582</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>2527283.895344466</v>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331155443_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>195232967.6952768</v>
+      </c>
+      <c r="B226" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C226" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D226" t="n">
+        <v>9375333.418723509</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="n">
+        <v>23664313.47821799</v>
+      </c>
+      <c r="G226" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H226" t="n">
+        <v>156504523.0974238</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M226" t="n">
+        <v>195232967.6952768</v>
+      </c>
+      <c r="N226" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V226" t="n">
+        <v>3.809000015258789</v>
+      </c>
+      <c r="W226" t="n">
+        <v>190996492.8463081</v>
+      </c>
+      <c r="X226" t="n">
+        <v>195232967.6952768</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>4236474.848968625</v>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331161445_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>212587113.7204228</v>
+      </c>
+      <c r="B227" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C227" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D227" t="n">
+        <v>9370697.908208419</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" t="n">
+        <v>23659677.9677029</v>
+      </c>
+      <c r="G227" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H227" t="n">
+        <v>173768053.2263788</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>9207635.981582437</v>
+      </c>
+      <c r="M227" t="n">
+        <v>212587113.7204228</v>
+      </c>
+      <c r="N227" t="n">
+        <v>61391.06622803005</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>61391.06622803005</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>61384.23987721652</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="n">
+        <v>6.826350813931863</v>
+      </c>
+      <c r="V227" t="n">
+        <v>3.183000087738037</v>
+      </c>
+      <c r="W227" t="n">
+        <v>208350638.8714543</v>
+      </c>
+      <c r="X227" t="n">
+        <v>212587113.7204228</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>4236474.848968506</v>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331161738_mea_inflex_std_1_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>225573626.2495907</v>
+      </c>
+      <c r="B228" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C228" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D228" t="n">
+        <v>9339987.651045963</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" t="n">
+        <v>23628967.71054045</v>
+      </c>
+      <c r="G228" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H228" t="n">
+        <v>186154235.4432818</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>9838676.551009862</v>
+      </c>
+      <c r="M228" t="n">
+        <v>225573626.2495907</v>
+      </c>
+      <c r="N228" t="n">
+        <v>65597.95077083209</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>65597.95077083209</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>65591.17700673267</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
+      <c r="T228" t="n">
+        <v>0</v>
+      </c>
+      <c r="U228" t="n">
+        <v>6.773764099812912</v>
+      </c>
+      <c r="V228" t="n">
+        <v>3.106000185012817</v>
+      </c>
+      <c r="W228" t="n">
+        <v>221337151.400622</v>
+      </c>
+      <c r="X228" t="n">
+        <v>225573626.2495907</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>4236474.848968714</v>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331161945_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>195076261.645486</v>
+      </c>
+      <c r="B229" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C229" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D229" t="n">
+        <v>9375333.418723509</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" t="n">
+        <v>23664313.47821799</v>
+      </c>
+      <c r="G229" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H229" t="n">
+        <v>156347817.047633</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M229" t="n">
+        <v>195076261.645486</v>
+      </c>
+      <c r="N229" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="n">
+        <v>0</v>
+      </c>
+      <c r="T229" t="n">
+        <v>0</v>
+      </c>
+      <c r="U229" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V229" t="n">
+        <v>3.730999946594238</v>
+      </c>
+      <c r="W229" t="n">
+        <v>190839786.7965176</v>
+      </c>
+      <c r="X229" t="n">
+        <v>195076261.645486</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>4236474.848968327</v>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331162250_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>212091020.4761293</v>
+      </c>
+      <c r="B230" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C230" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D230" t="n">
+        <v>9339408.212231576</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" t="n">
+        <v>23628388.27172606</v>
+      </c>
+      <c r="G230" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H230" t="n">
+        <v>172660302.6827965</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>9850582.976848116</v>
+      </c>
+      <c r="M230" t="n">
+        <v>212091020.4761293</v>
+      </c>
+      <c r="N230" t="n">
+        <v>65677.32595088494</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>65677.32595088494</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>65670.55317898768</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" t="n">
+        <v>6.772771897659724</v>
+      </c>
+      <c r="V230" t="n">
+        <v>3.085000038146973</v>
+      </c>
+      <c r="W230" t="n">
+        <v>207854545.6271607</v>
+      </c>
+      <c r="X230" t="n">
+        <v>212091020.4761293</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>4236474.848968655</v>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331162457_mea_inflex_std_2_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>223816142.8006546</v>
+      </c>
+      <c r="B231" t="n">
+        <v>14288980.05949448</v>
+      </c>
+      <c r="C231" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D231" t="n">
+        <v>9038100.028750874</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="n">
+        <v>23327080.08824536</v>
+      </c>
+      <c r="G231" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H231" t="n">
+        <v>178495391.7549107</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>16041924.4127399</v>
+      </c>
+      <c r="M231" t="n">
+        <v>223816142.8006546</v>
+      </c>
+      <c r="N231" t="n">
+        <v>106952.4195783769</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>106952.4195783769</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>106946.162751599</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" t="n">
+        <v>0</v>
+      </c>
+      <c r="U231" t="n">
+        <v>6.256826778002083</v>
+      </c>
+      <c r="V231" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="W231" t="n">
+        <v>219579667.9516861</v>
+      </c>
+      <c r="X231" t="n">
+        <v>223816142.8006546</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>4236474.848968536</v>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331162810_mea_inflex_std_2_el_price_150</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE231"/>
+  <dimension ref="A1:AE243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24272,6 +24272,1242 @@
       <c r="AE231" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260331162810_mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>198380143.7954721</v>
+      </c>
+      <c r="B232" t="n">
+        <v>15822294.2146771</v>
+      </c>
+      <c r="C232" t="n">
+        <v>5950072.294242878</v>
+      </c>
+      <c r="D232" t="n">
+        <v>9948608.915923037</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="n">
+        <v>25770903.13060014</v>
+      </c>
+      <c r="G232" t="n">
+        <v>5950072.294242878</v>
+      </c>
+      <c r="H232" t="n">
+        <v>157546783.7957529</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="n">
+        <v>9112384.574876238</v>
+      </c>
+      <c r="M232" t="n">
+        <v>198380143.7954721</v>
+      </c>
+      <c r="N232" t="n">
+        <v>60756.06478760556</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>60756.06478760556</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>60749.23049917545</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="n">
+        <v>0</v>
+      </c>
+      <c r="T232" t="n">
+        <v>0</v>
+      </c>
+      <c r="U232" t="n">
+        <v>6.834288431157251</v>
+      </c>
+      <c r="V232" t="n">
+        <v>10462.08700013161</v>
+      </c>
+      <c r="W232" t="n">
+        <v>193542247.1490416</v>
+      </c>
+      <c r="X232" t="n">
+        <v>198380143.7954721</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>4837896.646430582</v>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260424213421_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>216929866.9238391</v>
+      </c>
+      <c r="B233" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C233" t="n">
+        <v>5951746.544758596</v>
+      </c>
+      <c r="D233" t="n">
+        <v>9943373.656616133</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" t="n">
+        <v>25771928.34622888</v>
+      </c>
+      <c r="G233" t="n">
+        <v>5951746.544758596</v>
+      </c>
+      <c r="H233" t="n">
+        <v>175939023.922078</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>9267168.110773632</v>
+      </c>
+      <c r="M233" t="n">
+        <v>216929866.9238391</v>
+      </c>
+      <c r="N233" t="n">
+        <v>61787.94212829431</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>61787.94212829431</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>61781.12073849125</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
+      <c r="S233" t="n">
+        <v>0</v>
+      </c>
+      <c r="T233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="n">
+        <v>6.821389803165927</v>
+      </c>
+      <c r="V233" t="n">
+        <v>1342.444999933243</v>
+      </c>
+      <c r="W233" t="n">
+        <v>212187783.2033313</v>
+      </c>
+      <c r="X233" t="n">
+        <v>216929866.9238391</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>4742083.720507801</v>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425003144_mea_std_1_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>232401125.9793854</v>
+      </c>
+      <c r="B234" t="n">
+        <v>0</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>141277280.2306274</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>91123845.74875793</v>
+      </c>
+      <c r="M234" t="n">
+        <v>232401125.9793854</v>
+      </c>
+      <c r="N234" t="n">
+        <v>607492.3049917968</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>607492.3049917968</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>607492.3049917665</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="n">
+        <v>0</v>
+      </c>
+      <c r="T234" t="n">
+        <v>0</v>
+      </c>
+      <c r="U234" t="n">
+        <v>0</v>
+      </c>
+      <c r="V234" t="n">
+        <v>2153.633999824524</v>
+      </c>
+      <c r="W234" t="n">
+        <v>226084153.7089693</v>
+      </c>
+      <c r="X234" t="n">
+        <v>232401125.9793854</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>6316972.270416081</v>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425005652_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>198225520.6663301</v>
+      </c>
+      <c r="B235" t="n">
+        <v>15828554.68961276</v>
+      </c>
+      <c r="C235" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="D235" t="n">
+        <v>9950906.361202728</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="n">
+        <v>25779461.05081549</v>
+      </c>
+      <c r="G235" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="H235" t="n">
+        <v>157381928.4958803</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M235" t="n">
+        <v>198225520.6663301</v>
+      </c>
+      <c r="N235" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>60749.23049917664</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="n">
+        <v>0</v>
+      </c>
+      <c r="T235" t="n">
+        <v>0</v>
+      </c>
+      <c r="U235" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V235" t="n">
+        <v>914.0090000629425</v>
+      </c>
+      <c r="W235" t="n">
+        <v>193458936.7299272</v>
+      </c>
+      <c r="X235" t="n">
+        <v>198225520.6663301</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>4766583.936402828</v>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425013547_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>215851260.926798</v>
+      </c>
+      <c r="B236" t="n">
+        <v>15822294.21472696</v>
+      </c>
+      <c r="C236" t="n">
+        <v>5950072.294242923</v>
+      </c>
+      <c r="D236" t="n">
+        <v>9904011.551154803</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" t="n">
+        <v>25726305.76588176</v>
+      </c>
+      <c r="G236" t="n">
+        <v>5950072.294242923</v>
+      </c>
+      <c r="H236" t="n">
+        <v>174146102.6292823</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>10028780.23739106</v>
+      </c>
+      <c r="M236" t="n">
+        <v>215851260.926798</v>
+      </c>
+      <c r="N236" t="n">
+        <v>66865.29283806655</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>66865.29283806655</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>66858.53491594146</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="n">
+        <v>0</v>
+      </c>
+      <c r="T236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="n">
+        <v>6.757922125947767</v>
+      </c>
+      <c r="V236" t="n">
+        <v>1621.40499997139</v>
+      </c>
+      <c r="W236" t="n">
+        <v>211429752.3127332</v>
+      </c>
+      <c r="X236" t="n">
+        <v>215851260.926798</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>4421508.614064842</v>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425015348_mea_std_2_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>226659646.0685059</v>
+      </c>
+      <c r="B237" t="n">
+        <v>15834820.84864306</v>
+      </c>
+      <c r="C237" t="n">
+        <v>5953422.254316006</v>
+      </c>
+      <c r="D237" t="n">
+        <v>9599594.119778559</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="n">
+        <v>25434414.96842162</v>
+      </c>
+      <c r="G237" t="n">
+        <v>5953422.254316006</v>
+      </c>
+      <c r="H237" t="n">
+        <v>178893339.8386377</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" t="n">
+        <v>16378469.00713065</v>
+      </c>
+      <c r="M237" t="n">
+        <v>226659646.0685059</v>
+      </c>
+      <c r="N237" t="n">
+        <v>109196.0221622654</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>109196.0221622654</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>109189.7933808706</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" t="n">
+        <v>0</v>
+      </c>
+      <c r="T237" t="n">
+        <v>0</v>
+      </c>
+      <c r="U237" t="n">
+        <v>6.228781395136024</v>
+      </c>
+      <c r="V237" t="n">
+        <v>7548.073000192642</v>
+      </c>
+      <c r="W237" t="n">
+        <v>223495083.2110209</v>
+      </c>
+      <c r="X237" t="n">
+        <v>226659646.0685059</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>3164562.857484996</v>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425022343_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>198392979.5859249</v>
+      </c>
+      <c r="B238" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C238" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D238" t="n">
+        <v>9950906.361203149</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" t="n">
+        <v>25779461.0508159</v>
+      </c>
+      <c r="G238" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H238" t="n">
+        <v>157549387.415474</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M238" t="n">
+        <v>198392979.5859249</v>
+      </c>
+      <c r="N238" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="n">
+        <v>0</v>
+      </c>
+      <c r="T238" t="n">
+        <v>0</v>
+      </c>
+      <c r="U238" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V238" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="W238" t="n">
+        <v>194156504.7369564</v>
+      </c>
+      <c r="X238" t="n">
+        <v>198392979.5859249</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>4236474.848968536</v>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425043234_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>216929866.9238383</v>
+      </c>
+      <c r="B239" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C239" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D239" t="n">
+        <v>9943373.656616133</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" t="n">
+        <v>25771928.34622888</v>
+      </c>
+      <c r="G239" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H239" t="n">
+        <v>175939023.9220771</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" t="n">
+        <v>9267168.110773703</v>
+      </c>
+      <c r="M239" t="n">
+        <v>216929866.9238383</v>
+      </c>
+      <c r="N239" t="n">
+        <v>61787.94212829439</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" t="n">
+        <v>61787.94212829439</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>61781.12073849163</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" t="n">
+        <v>0</v>
+      </c>
+      <c r="T239" t="n">
+        <v>0</v>
+      </c>
+      <c r="U239" t="n">
+        <v>6.821389803165925</v>
+      </c>
+      <c r="V239" t="n">
+        <v>3.453999996185303</v>
+      </c>
+      <c r="W239" t="n">
+        <v>212693392.0748695</v>
+      </c>
+      <c r="X239" t="n">
+        <v>216929866.9238383</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>4236474.848968774</v>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425043550_mea_inflex_std_1_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>230740725.8105568</v>
+      </c>
+      <c r="B240" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C240" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D240" t="n">
+        <v>9872102.682446657</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="n">
+        <v>25700657.3720594</v>
+      </c>
+      <c r="G240" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H240" t="n">
+        <v>188356663.4048599</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="n">
+        <v>10731658.48887887</v>
+      </c>
+      <c r="M240" t="n">
+        <v>230740725.8105568</v>
+      </c>
+      <c r="N240" t="n">
+        <v>71551.08927479727</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>71551.08927479727</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>71544.3899258593</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
+        <v>0</v>
+      </c>
+      <c r="U240" t="n">
+        <v>6.699348938323829</v>
+      </c>
+      <c r="V240" t="n">
+        <v>3.233000040054321</v>
+      </c>
+      <c r="W240" t="n">
+        <v>226504250.9615883</v>
+      </c>
+      <c r="X240" t="n">
+        <v>230740725.8105568</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>4236474.848968476</v>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425043804_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>198225520.6663415</v>
+      </c>
+      <c r="B241" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C241" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D241" t="n">
+        <v>9950906.361203149</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F241" t="n">
+        <v>25779461.0508159</v>
+      </c>
+      <c r="G241" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H241" t="n">
+        <v>157381928.4958906</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M241" t="n">
+        <v>198225520.6663415</v>
+      </c>
+      <c r="N241" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="n">
+        <v>0</v>
+      </c>
+      <c r="T241" t="n">
+        <v>0</v>
+      </c>
+      <c r="U241" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V241" t="n">
+        <v>4.746999979019165</v>
+      </c>
+      <c r="W241" t="n">
+        <v>193989045.817373</v>
+      </c>
+      <c r="X241" t="n">
+        <v>198225520.6663415</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>4236474.848968416</v>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425044130_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>216339245.2149234</v>
+      </c>
+      <c r="B242" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C242" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D242" t="n">
+        <v>9883112.019919991</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" t="n">
+        <v>25711666.70953274</v>
+      </c>
+      <c r="G242" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H242" t="n">
+        <v>174170395.56268</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>10505436.39795206</v>
+      </c>
+      <c r="M242" t="n">
+        <v>216339245.2149234</v>
+      </c>
+      <c r="N242" t="n">
+        <v>70042.96085379274</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>70042.96085379274</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>70036.24265301388</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="n">
+        <v>0</v>
+      </c>
+      <c r="T242" t="n">
+        <v>0</v>
+      </c>
+      <c r="U242" t="n">
+        <v>6.718200779234397</v>
+      </c>
+      <c r="V242" t="n">
+        <v>3.592000007629395</v>
+      </c>
+      <c r="W242" t="n">
+        <v>212102770.365955</v>
+      </c>
+      <c r="X242" t="n">
+        <v>216339245.2149234</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>4236474.848968446</v>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425044346_mea_inflex_std_2_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>228409984.2613358</v>
+      </c>
+      <c r="B243" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C243" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D243" t="n">
+        <v>9496046.891910162</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" t="n">
+        <v>25324601.58152291</v>
+      </c>
+      <c r="G243" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H243" t="n">
+        <v>178674707.2771491</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>18458928.85790531</v>
+      </c>
+      <c r="M243" t="n">
+        <v>228409984.2613358</v>
+      </c>
+      <c r="N243" t="n">
+        <v>123065.5811291093</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>123065.5811291093</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>123059.5257193684</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
+      <c r="T243" t="n">
+        <v>0</v>
+      </c>
+      <c r="U243" t="n">
+        <v>6.055409740904965</v>
+      </c>
+      <c r="V243" t="n">
+        <v>3.569999933242798</v>
+      </c>
+      <c r="W243" t="n">
+        <v>224173509.4123673</v>
+      </c>
+      <c r="X243" t="n">
+        <v>228409984.2613358</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>4236474.848968565</v>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425044731_mea_inflex_std_2_el_price_150</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE243"/>
+  <dimension ref="A1:AE255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25508,6 +25508,1242 @@
       <c r="AE243" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260425044731_mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>202384204.0297108</v>
+      </c>
+      <c r="B244" t="n">
+        <v>15828554.68961276</v>
+      </c>
+      <c r="C244" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="D244" t="n">
+        <v>13942130.80499869</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" t="n">
+        <v>29770685.49461146</v>
+      </c>
+      <c r="G244" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="H244" t="n">
+        <v>157549387.4154651</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M244" t="n">
+        <v>202384204.0297108</v>
+      </c>
+      <c r="N244" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>60749.23049917664</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="n">
+        <v>0</v>
+      </c>
+      <c r="T244" t="n">
+        <v>0</v>
+      </c>
+      <c r="U244" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V244" t="n">
+        <v>1239.359999895096</v>
+      </c>
+      <c r="W244" t="n">
+        <v>197529266.3848676</v>
+      </c>
+      <c r="X244" t="n">
+        <v>202384204.0297108</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>4854937.644843251</v>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428190721_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>220584021.3102081</v>
+      </c>
+      <c r="B245" t="n">
+        <v>15832731.56036155</v>
+      </c>
+      <c r="C245" t="n">
+        <v>5952863.522230169</v>
+      </c>
+      <c r="D245" t="n">
+        <v>13928593.66829422</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" t="n">
+        <v>29761325.22865577</v>
+      </c>
+      <c r="G245" t="n">
+        <v>5952863.522230169</v>
+      </c>
+      <c r="H245" t="n">
+        <v>175602619.4925406</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="n">
+        <v>9267213.066781623</v>
+      </c>
+      <c r="M245" t="n">
+        <v>220584021.3102081</v>
+      </c>
+      <c r="N245" t="n">
+        <v>61788.24183127812</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="n">
+        <v>61788.24183127812</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>61781.42044521334</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0</v>
+      </c>
+      <c r="S245" t="n">
+        <v>0</v>
+      </c>
+      <c r="T245" t="n">
+        <v>0</v>
+      </c>
+      <c r="U245" t="n">
+        <v>6.821386056832006</v>
+      </c>
+      <c r="V245" t="n">
+        <v>2348.817000150681</v>
+      </c>
+      <c r="W245" t="n">
+        <v>216176728.1893944</v>
+      </c>
+      <c r="X245" t="n">
+        <v>220584021.3102081</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>4407293.120813757</v>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428193100_mea_std_1_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>232401125.9793854</v>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>141277280.2306274</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" t="n">
+        <v>91123845.74875793</v>
+      </c>
+      <c r="M246" t="n">
+        <v>232401125.9793854</v>
+      </c>
+      <c r="N246" t="n">
+        <v>607492.3049917968</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="n">
+        <v>607492.3049917968</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>607492.3049917665</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="n">
+        <v>0</v>
+      </c>
+      <c r="T246" t="n">
+        <v>0</v>
+      </c>
+      <c r="U246" t="n">
+        <v>0</v>
+      </c>
+      <c r="V246" t="n">
+        <v>2557.744999885559</v>
+      </c>
+      <c r="W246" t="n">
+        <v>229989480.0472538</v>
+      </c>
+      <c r="X246" t="n">
+        <v>232401125.9793854</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>2411645.932131559</v>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428201255_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>202216745.110126</v>
+      </c>
+      <c r="B247" t="n">
+        <v>15828554.68961276</v>
+      </c>
+      <c r="C247" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="D247" t="n">
+        <v>13942130.80499869</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="n">
+        <v>29770685.49461146</v>
+      </c>
+      <c r="G247" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="H247" t="n">
+        <v>157381928.4958803</v>
+      </c>
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" t="n">
+        <v>9112384.574875711</v>
+      </c>
+      <c r="M247" t="n">
+        <v>202216745.110126</v>
+      </c>
+      <c r="N247" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>60749.23049917664</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0</v>
+      </c>
+      <c r="S247" t="n">
+        <v>0</v>
+      </c>
+      <c r="T247" t="n">
+        <v>0</v>
+      </c>
+      <c r="U247" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V247" t="n">
+        <v>1382.749000072479</v>
+      </c>
+      <c r="W247" t="n">
+        <v>197455019.7009251</v>
+      </c>
+      <c r="X247" t="n">
+        <v>202216745.110126</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>4761725.409200966</v>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428205835_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>220892029.5268725</v>
+      </c>
+      <c r="B248" t="n">
+        <v>15828554.68961273</v>
+      </c>
+      <c r="C248" t="n">
+        <v>5951746.54475859</v>
+      </c>
+      <c r="D248" t="n">
+        <v>13615325.27113798</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" t="n">
+        <v>29443879.96075071</v>
+      </c>
+      <c r="G248" t="n">
+        <v>5951746.54475859</v>
+      </c>
+      <c r="H248" t="n">
+        <v>173026406.3600993</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>0</v>
+      </c>
+      <c r="L248" t="n">
+        <v>12469996.66126391</v>
+      </c>
+      <c r="M248" t="n">
+        <v>220892029.5268725</v>
+      </c>
+      <c r="N248" t="n">
+        <v>83139.86556251612</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="n">
+        <v>83139.86556251612</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>83133.31107509247</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0</v>
+      </c>
+      <c r="S248" t="n">
+        <v>0</v>
+      </c>
+      <c r="T248" t="n">
+        <v>0</v>
+      </c>
+      <c r="U248" t="n">
+        <v>6.554487423958414</v>
+      </c>
+      <c r="V248" t="n">
+        <v>1461.787000179291</v>
+      </c>
+      <c r="W248" t="n">
+        <v>215374588.4597989</v>
+      </c>
+      <c r="X248" t="n">
+        <v>220892029.5268725</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>5517441.067073673</v>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428212424_mea_std_2_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>232401125.9793854</v>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>141277280.2306274</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L249" t="n">
+        <v>91123845.74875793</v>
+      </c>
+      <c r="M249" t="n">
+        <v>232401125.9793854</v>
+      </c>
+      <c r="N249" t="n">
+        <v>607492.3049917968</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="n">
+        <v>607492.3049917968</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>607492.3049917665</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0</v>
+      </c>
+      <c r="S249" t="n">
+        <v>0</v>
+      </c>
+      <c r="T249" t="n">
+        <v>0</v>
+      </c>
+      <c r="U249" t="n">
+        <v>0</v>
+      </c>
+      <c r="V249" t="n">
+        <v>810.7369999885559</v>
+      </c>
+      <c r="W249" t="n">
+        <v>227153275.6748863</v>
+      </c>
+      <c r="X249" t="n">
+        <v>232401125.9793854</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>5247850.30449903</v>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428215138_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>202384204.0297208</v>
+      </c>
+      <c r="B250" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C250" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D250" t="n">
+        <v>13942130.80499909</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" t="n">
+        <v>29770685.49461184</v>
+      </c>
+      <c r="G250" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H250" t="n">
+        <v>157549387.415474</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M250" t="n">
+        <v>202384204.0297208</v>
+      </c>
+      <c r="N250" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" t="n">
+        <v>0</v>
+      </c>
+      <c r="T250" t="n">
+        <v>0</v>
+      </c>
+      <c r="U250" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V250" t="n">
+        <v>3.235000133514404</v>
+      </c>
+      <c r="W250" t="n">
+        <v>198147729.1807524</v>
+      </c>
+      <c r="X250" t="n">
+        <v>202384204.0297208</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>4236474.848968476</v>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428220813_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>220913384.9876675</v>
+      </c>
+      <c r="B251" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C251" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D251" t="n">
+        <v>13925906.41679323</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" t="n">
+        <v>29754461.10640598</v>
+      </c>
+      <c r="G251" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H251" t="n">
+        <v>175928102.799891</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0</v>
+      </c>
+      <c r="L251" t="n">
+        <v>9279074.536611956</v>
+      </c>
+      <c r="M251" t="n">
+        <v>220913384.9876675</v>
+      </c>
+      <c r="N251" t="n">
+        <v>61867.31730834726</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="n">
+        <v>61867.31730834726</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>61860.49691074665</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0</v>
+      </c>
+      <c r="S251" t="n">
+        <v>0</v>
+      </c>
+      <c r="T251" t="n">
+        <v>0</v>
+      </c>
+      <c r="U251" t="n">
+        <v>6.820397601012736</v>
+      </c>
+      <c r="V251" t="n">
+        <v>3.228999853134155</v>
+      </c>
+      <c r="W251" t="n">
+        <v>216676910.138699</v>
+      </c>
+      <c r="X251" t="n">
+        <v>220913384.9876675</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>4236474.848968565</v>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428221126_mea_inflex_std_1_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>232401125.979409</v>
+      </c>
+      <c r="B252" t="n">
+        <v>0</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>141277280.2306451</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L252" t="n">
+        <v>91123845.74876392</v>
+      </c>
+      <c r="M252" t="n">
+        <v>232401125.979409</v>
+      </c>
+      <c r="N252" t="n">
+        <v>607492.3049917679</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
+        <v>607492.3049917679</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>607492.3049917656</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0</v>
+      </c>
+      <c r="S252" t="n">
+        <v>0</v>
+      </c>
+      <c r="T252" t="n">
+        <v>0</v>
+      </c>
+      <c r="U252" t="n">
+        <v>0</v>
+      </c>
+      <c r="V252" t="n">
+        <v>3.773000001907349</v>
+      </c>
+      <c r="W252" t="n">
+        <v>232401125.979409</v>
+      </c>
+      <c r="X252" t="n">
+        <v>232401125.979409</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428221338_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>202216745.1101374</v>
+      </c>
+      <c r="B253" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C253" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D253" t="n">
+        <v>13942130.80499909</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" t="n">
+        <v>29770685.49461184</v>
+      </c>
+      <c r="G253" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H253" t="n">
+        <v>157381928.4958906</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" t="n">
+        <v>9112384.574876411</v>
+      </c>
+      <c r="M253" t="n">
+        <v>202216745.1101374</v>
+      </c>
+      <c r="N253" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0</v>
+      </c>
+      <c r="S253" t="n">
+        <v>0</v>
+      </c>
+      <c r="T253" t="n">
+        <v>0</v>
+      </c>
+      <c r="U253" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V253" t="n">
+        <v>3.990000009536743</v>
+      </c>
+      <c r="W253" t="n">
+        <v>197980270.261169</v>
+      </c>
+      <c r="X253" t="n">
+        <v>202216745.1101374</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>4236474.848968416</v>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428221706_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>220247366.3896451</v>
+      </c>
+      <c r="B254" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C254" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D254" t="n">
+        <v>13739325.95242576</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" t="n">
+        <v>29567880.64203851</v>
+      </c>
+      <c r="G254" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H254" t="n">
+        <v>173531730.1062772</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="n">
+        <v>11196009.09657076</v>
+      </c>
+      <c r="M254" t="n">
+        <v>220247366.3896451</v>
+      </c>
+      <c r="N254" t="n">
+        <v>74646.72129685915</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>74646.72129685915</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>74640.06064380513</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0</v>
+      </c>
+      <c r="S254" t="n">
+        <v>0</v>
+      </c>
+      <c r="T254" t="n">
+        <v>0</v>
+      </c>
+      <c r="U254" t="n">
+        <v>6.660653054349505</v>
+      </c>
+      <c r="V254" t="n">
+        <v>3.496000051498413</v>
+      </c>
+      <c r="W254" t="n">
+        <v>216010891.5406764</v>
+      </c>
+      <c r="X254" t="n">
+        <v>220247366.3896451</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>4236474.848968655</v>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428221919_mea_inflex_std_2_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>231905367.7318483</v>
+      </c>
+      <c r="B255" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C255" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D255" t="n">
+        <v>12841190.17674384</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="n">
+        <v>28669744.86635659</v>
+      </c>
+      <c r="G255" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H255" t="n">
+        <v>176860387.199516</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="n">
+        <v>20423489.12121709</v>
+      </c>
+      <c r="M255" t="n">
+        <v>231905367.7318483</v>
+      </c>
+      <c r="N255" t="n">
+        <v>136162.4858378327</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>136162.4858378327</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>136156.5941414469</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0</v>
+      </c>
+      <c r="S255" t="n">
+        <v>0</v>
+      </c>
+      <c r="T255" t="n">
+        <v>0</v>
+      </c>
+      <c r="U255" t="n">
+        <v>5.891696385628983</v>
+      </c>
+      <c r="V255" t="n">
+        <v>3.160000085830688</v>
+      </c>
+      <c r="W255" t="n">
+        <v>227668892.8828797</v>
+      </c>
+      <c r="X255" t="n">
+        <v>231905367.7318483</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>4236474.848968595</v>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428222302_mea_inflex_std_2_el_price_150</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/flexible_ops/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE255"/>
+  <dimension ref="A1:AE267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26744,6 +26744,1242 @@
       <c r="AE255" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260428222302_mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>205421665.5546794</v>
+      </c>
+      <c r="B256" t="n">
+        <v>15828554.68961267</v>
+      </c>
+      <c r="C256" t="n">
+        <v>5951746.544758577</v>
+      </c>
+      <c r="D256" t="n">
+        <v>13942130.80499887</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="n">
+        <v>29770685.49461155</v>
+      </c>
+      <c r="G256" t="n">
+        <v>5951746.544758577</v>
+      </c>
+      <c r="H256" t="n">
+        <v>157549387.4154739</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" t="n">
+        <v>12149846.09983538</v>
+      </c>
+      <c r="M256" t="n">
+        <v>205421665.5546794</v>
+      </c>
+      <c r="N256" t="n">
+        <v>60756.06478760712</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>60756.06478760712</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>60749.23049917621</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="n">
+        <v>0</v>
+      </c>
+      <c r="T256" t="n">
+        <v>0</v>
+      </c>
+      <c r="U256" t="n">
+        <v>6.83428843115733</v>
+      </c>
+      <c r="V256" t="n">
+        <v>1098.470999956131</v>
+      </c>
+      <c r="W256" t="n">
+        <v>200573407.8761249</v>
+      </c>
+      <c r="X256" t="n">
+        <v>205421665.5546794</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>4848257.678554475</v>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429152345_mea_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>223981243.2819453</v>
+      </c>
+      <c r="B257" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C257" t="n">
+        <v>5951746.544758596</v>
+      </c>
+      <c r="D257" t="n">
+        <v>13940971.92012725</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" t="n">
+        <v>29769526.60974</v>
+      </c>
+      <c r="G257" t="n">
+        <v>5951746.544758596</v>
+      </c>
+      <c r="H257" t="n">
+        <v>176094248.799438</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>12165721.3280087</v>
+      </c>
+      <c r="M257" t="n">
+        <v>223981243.2819453</v>
+      </c>
+      <c r="N257" t="n">
+        <v>60835.43993627258</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>60835.43993627258</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>60828.60664004413</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="n">
+        <v>0</v>
+      </c>
+      <c r="T257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="n">
+        <v>6.833296229004181</v>
+      </c>
+      <c r="V257" t="n">
+        <v>1245.147000074387</v>
+      </c>
+      <c r="W257" t="n">
+        <v>219218853.0545272</v>
+      </c>
+      <c r="X257" t="n">
+        <v>223981243.2819453</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>4762390.227418125</v>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429154501_mea_std_1_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>238489453.2328438</v>
+      </c>
+      <c r="B258" t="n">
+        <v>15828554.68961281</v>
+      </c>
+      <c r="C258" t="n">
+        <v>5951746.544758609</v>
+      </c>
+      <c r="D258" t="n">
+        <v>13833195.62704545</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="n">
+        <v>29661750.31665826</v>
+      </c>
+      <c r="G258" t="n">
+        <v>5951746.544758609</v>
+      </c>
+      <c r="H258" t="n">
+        <v>189233838.2331971</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
+        <v>13642118.13822984</v>
+      </c>
+      <c r="M258" t="n">
+        <v>238489453.2328438</v>
+      </c>
+      <c r="N258" t="n">
+        <v>68217.33171257694</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>68217.33171257694</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>68210.59069114873</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
+        <v>0</v>
+      </c>
+      <c r="U258" t="n">
+        <v>6.741021428757747</v>
+      </c>
+      <c r="V258" t="n">
+        <v>1407.786000013351</v>
+      </c>
+      <c r="W258" t="n">
+        <v>233194162.9131742</v>
+      </c>
+      <c r="X258" t="n">
+        <v>238489453.2328438</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>5295290.319669634</v>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>mea_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429160831_mea_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>205254206.6350865</v>
+      </c>
+      <c r="B259" t="n">
+        <v>15828554.68961276</v>
+      </c>
+      <c r="C259" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="D259" t="n">
+        <v>13942130.80499869</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="n">
+        <v>29770685.49461146</v>
+      </c>
+      <c r="G259" t="n">
+        <v>5951746.544758598</v>
+      </c>
+      <c r="H259" t="n">
+        <v>157381928.4958803</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>12149846.09983613</v>
+      </c>
+      <c r="M259" t="n">
+        <v>205254206.6350865</v>
+      </c>
+      <c r="N259" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>60756.06478762635</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>60749.23049917664</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="n">
+        <v>0</v>
+      </c>
+      <c r="T259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="n">
+        <v>6.834288431157373</v>
+      </c>
+      <c r="V259" t="n">
+        <v>2254.676000118256</v>
+      </c>
+      <c r="W259" t="n">
+        <v>200492409.5668638</v>
+      </c>
+      <c r="X259" t="n">
+        <v>205254206.6350865</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>4761797.068222642</v>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429163459_mea_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>223606365.1051984</v>
+      </c>
+      <c r="B260" t="n">
+        <v>15828554.68961272</v>
+      </c>
+      <c r="C260" t="n">
+        <v>5951746.544758588</v>
+      </c>
+      <c r="D260" t="n">
+        <v>13903887.60422809</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" t="n">
+        <v>29732442.29384081</v>
+      </c>
+      <c r="G260" t="n">
+        <v>5951746.544758588</v>
+      </c>
+      <c r="H260" t="n">
+        <v>175248447.4298804</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" t="n">
+        <v>12673728.83671858</v>
+      </c>
+      <c r="M260" t="n">
+        <v>223606365.1051984</v>
+      </c>
+      <c r="N260" t="n">
+        <v>63375.44572935176</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>63375.44572935176</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>63368.64418359224</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0</v>
+      </c>
+      <c r="S260" t="n">
+        <v>0</v>
+      </c>
+      <c r="T260" t="n">
+        <v>0</v>
+      </c>
+      <c r="U260" t="n">
+        <v>6.801545760102169</v>
+      </c>
+      <c r="V260" t="n">
+        <v>1312.77899980545</v>
+      </c>
+      <c r="W260" t="n">
+        <v>218513834.8607792</v>
+      </c>
+      <c r="X260" t="n">
+        <v>223606365.1051984</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>5092530.244419158</v>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429171522_mea_std_2_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>231975055.1470265</v>
+      </c>
+      <c r="B261" t="n">
+        <v>15822294.24051538</v>
+      </c>
+      <c r="C261" t="n">
+        <v>5950072.294243124</v>
+      </c>
+      <c r="D261" t="n">
+        <v>13872647.29937306</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" t="n">
+        <v>29694941.53988845</v>
+      </c>
+      <c r="G261" t="n">
+        <v>5950072.294243124</v>
+      </c>
+      <c r="H261" t="n">
+        <v>183259832.469755</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" t="n">
+        <v>13070208.84313998</v>
+      </c>
+      <c r="M261" t="n">
+        <v>231975055.1470265</v>
+      </c>
+      <c r="N261" t="n">
+        <v>65357.82098145759</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>65357.82098145759</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>65351.04421570416</v>
+      </c>
+      <c r="R261" t="n">
+        <v>0</v>
+      </c>
+      <c r="S261" t="n">
+        <v>0</v>
+      </c>
+      <c r="T261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="n">
+        <v>6.776765759701132</v>
+      </c>
+      <c r="V261" t="n">
+        <v>3742.485000133514</v>
+      </c>
+      <c r="W261" t="n">
+        <v>231248148.7047271</v>
+      </c>
+      <c r="X261" t="n">
+        <v>231975055.1470265</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>726906.4422993958</v>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>mea_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429174009_mea_std_2_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>205421665.5546798</v>
+      </c>
+      <c r="B262" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C262" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D262" t="n">
+        <v>13942130.80499909</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
+        <v>29770685.49461184</v>
+      </c>
+      <c r="G262" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H262" t="n">
+        <v>157549387.415474</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="n">
+        <v>12149846.09983537</v>
+      </c>
+      <c r="M262" t="n">
+        <v>205421665.5546798</v>
+      </c>
+      <c r="N262" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0</v>
+      </c>
+      <c r="S262" t="n">
+        <v>0</v>
+      </c>
+      <c r="T262" t="n">
+        <v>0</v>
+      </c>
+      <c r="U262" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V262" t="n">
+        <v>3.588000059127808</v>
+      </c>
+      <c r="W262" t="n">
+        <v>201185190.7056794</v>
+      </c>
+      <c r="X262" t="n">
+        <v>205421665.5546798</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>4236474.849000394</v>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429184535_mea_inflex_std_1_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>223971867.7453849</v>
+      </c>
+      <c r="B263" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C263" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D263" t="n">
+        <v>13942130.80499909</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" t="n">
+        <v>29770685.49461184</v>
+      </c>
+      <c r="G263" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H263" t="n">
+        <v>176099589.6061791</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" t="n">
+        <v>12149846.09983537</v>
+      </c>
+      <c r="M263" t="n">
+        <v>223971867.7453849</v>
+      </c>
+      <c r="N263" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0</v>
+      </c>
+      <c r="S263" t="n">
+        <v>0</v>
+      </c>
+      <c r="T263" t="n">
+        <v>0</v>
+      </c>
+      <c r="U263" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V263" t="n">
+        <v>3.459000110626221</v>
+      </c>
+      <c r="W263" t="n">
+        <v>219735392.8963844</v>
+      </c>
+      <c r="X263" t="n">
+        <v>223971867.7453849</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>4236474.849000484</v>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429184851_mea_inflex_std_1_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>237930738.5200295</v>
+      </c>
+      <c r="B264" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C264" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D264" t="n">
+        <v>13922429.76217768</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" t="n">
+        <v>29750984.45179043</v>
+      </c>
+      <c r="G264" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H264" t="n">
+        <v>189808282.4379781</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>12419725.08550244</v>
+      </c>
+      <c r="M264" t="n">
+        <v>237930738.5200295</v>
+      </c>
+      <c r="N264" t="n">
+        <v>62105.44284850587</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>62105.44284850587</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>62098.62542751172</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0</v>
+      </c>
+      <c r="S264" t="n">
+        <v>0</v>
+      </c>
+      <c r="T264" t="n">
+        <v>0</v>
+      </c>
+      <c r="U264" t="n">
+        <v>6.817420994553173</v>
+      </c>
+      <c r="V264" t="n">
+        <v>3.455999851226807</v>
+      </c>
+      <c r="W264" t="n">
+        <v>233694263.671029</v>
+      </c>
+      <c r="X264" t="n">
+        <v>237930738.5200295</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>4236474.849000573</v>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429185105_mea_inflex_std_1_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>205254206.6350964</v>
+      </c>
+      <c r="B265" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C265" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D265" t="n">
+        <v>13942130.80499909</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" t="n">
+        <v>29770685.49461184</v>
+      </c>
+      <c r="G265" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H265" t="n">
+        <v>157381928.4958906</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="n">
+        <v>12149846.09983537</v>
+      </c>
+      <c r="M265" t="n">
+        <v>205254206.6350964</v>
+      </c>
+      <c r="N265" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>60756.06478760711</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>60749.23049917634</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0</v>
+      </c>
+      <c r="S265" t="n">
+        <v>0</v>
+      </c>
+      <c r="T265" t="n">
+        <v>0</v>
+      </c>
+      <c r="U265" t="n">
+        <v>6.834288431157366</v>
+      </c>
+      <c r="V265" t="n">
+        <v>4.41700005531311</v>
+      </c>
+      <c r="W265" t="n">
+        <v>201017731.7860957</v>
+      </c>
+      <c r="X265" t="n">
+        <v>205254206.6350964</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>4236474.849000633</v>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429185432_mea_inflex_std_2_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>223539324.7182135</v>
+      </c>
+      <c r="B266" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C266" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D266" t="n">
+        <v>13914317.56807475</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" t="n">
+        <v>29742872.2576875</v>
+      </c>
+      <c r="G266" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H266" t="n">
+        <v>175313854.189108</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
+        <v>12530851.72665947</v>
+      </c>
+      <c r="M266" t="n">
+        <v>223539324.7182135</v>
+      </c>
+      <c r="N266" t="n">
+        <v>62661.06910887594</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="n">
+        <v>62661.06910887594</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>62654.25863329686</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="n">
+        <v>0</v>
+      </c>
+      <c r="T266" t="n">
+        <v>0</v>
+      </c>
+      <c r="U266" t="n">
+        <v>6.810475579480859</v>
+      </c>
+      <c r="V266" t="n">
+        <v>3.53600001335144</v>
+      </c>
+      <c r="W266" t="n">
+        <v>219302849.8692129</v>
+      </c>
+      <c r="X266" t="n">
+        <v>223539324.7182135</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>4236474.849000663</v>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429185649_mea_inflex_std_2_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>236938141.4070603</v>
+      </c>
+      <c r="B267" t="n">
+        <v>15828554.68961275</v>
+      </c>
+      <c r="C267" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="D267" t="n">
+        <v>13704559.40627033</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" t="n">
+        <v>29533114.09588308</v>
+      </c>
+      <c r="G267" t="n">
+        <v>5951746.544758594</v>
+      </c>
+      <c r="H267" t="n">
+        <v>186049011.6041274</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L267" t="n">
+        <v>15404269.16229124</v>
+      </c>
+      <c r="M267" t="n">
+        <v>236938141.4070603</v>
+      </c>
+      <c r="N267" t="n">
+        <v>77027.97669844523</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="P267" t="n">
+        <v>77027.97669844523</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>77021.34581145579</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="n">
+        <v>0</v>
+      </c>
+      <c r="T267" t="n">
+        <v>0</v>
+      </c>
+      <c r="U267" t="n">
+        <v>6.630886989753872</v>
+      </c>
+      <c r="V267" t="n">
+        <v>3.631999969482422</v>
+      </c>
+      <c r="W267" t="n">
+        <v>232701666.5580599</v>
+      </c>
+      <c r="X267" t="n">
+        <v>236938141.4070603</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>4236474.849000424</v>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>mea_inflex_std_2_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\flexible_ops\20260429190033_mea_inflex_std_2_el_price_150</t>
         </is>
       </c>
     </row>
